--- a/EconAutomation/src/supporting_docs/econ_wb_templates/WorkingCalc_Current.xlsx
+++ b/EconAutomation/src/supporting_docs/econ_wb_templates/WorkingCalc_Current.xlsx
@@ -12,7 +12,7 @@
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACC5C77-3153-49AF-A98A-0B803BD0EF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" tabRatio="808" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDA883B1-89AA-41DF-A01F-246993B8D400}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{FDA883B1-89AA-41DF-A01F-246993B8D400}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORT_OUTPUTS" sheetId="30" r:id="rId1"/>
@@ -1463,10 +1463,10 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="#0.0"/>
-    <numFmt numFmtId="168" formatCode="#0.000"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="#0.0"/>
+    <numFmt numFmtId="167" formatCode="#0.000"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -2221,7 +2221,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2289,10 +2289,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2323,13 +2323,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2400,7 +2400,7 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="19" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2444,8 +2444,40 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2467,6 +2499,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2494,45 +2529,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -2541,6 +2537,76 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="116">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2653,76 +2719,6 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -5624,11 +5620,11 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{32BFE16E-A259-4C63-8DCF-00C9A6EFA78D}" name="Table15" displayName="Table15" ref="F1:G32" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{32BFE16E-A259-4C63-8DCF-00C9A6EFA78D}" name="Table15" displayName="Table15" ref="F1:G32" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="F1:G32" xr:uid="{32BFE16E-A259-4C63-8DCF-00C9A6EFA78D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{099144D5-37E0-4580-8BDC-BF9DA5901655}" name="PASTED YEAR" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{DEBA212E-45CC-4A41-A95A-1A261BC6D9AB}" name="PASTED DISCOUNT RATES" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{099144D5-37E0-4580-8BDC-BF9DA5901655}" name="PASTED YEAR" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{DEBA212E-45CC-4A41-A95A-1A261BC6D9AB}" name="PASTED DISCOUNT RATES" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6108,24 +6104,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="115" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="101"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="117"/>
       <c r="E1" s="56"/>
-      <c r="F1" s="102" t="str" cm="1">
+      <c r="F1" s="118" t="str" cm="1">
         <f t="array" aca="1" ref="F1" ca="1">_xlfn.TEXTAFTER(_xlfn.TEXTBEFORE(CELL("filename",A1),"]"),"[") &amp; " TABLES"</f>
         <v>WorkingCalc_Current.xlsx TABLES</v>
       </c>
-      <c r="G1" s="103"/>
+      <c r="G1" s="119"/>
       <c r="H1" s="56"/>
-      <c r="I1" s="104" t="str" cm="1">
+      <c r="I1" s="120" t="str" cm="1">
         <f t="array" aca="1" ref="I1" ca="1">_xlfn.TEXTAFTER(_xlfn.TEXTBEFORE(CELL("filename",D1),"]"),"[") &amp; " CHARTS"</f>
         <v>WorkingCalc_Current.xlsx CHARTS</v>
       </c>
-      <c r="J1" s="105"/>
+      <c r="J1" s="121"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="57" t="s">
@@ -6238,7 +6234,7 @@
       <c r="J6" s="76"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="130" t="s">
+      <c r="A7" s="110" t="s">
         <v>323</v>
       </c>
       <c r="B7" s="72" t="s">
@@ -6257,7 +6253,7 @@
       <c r="J7" s="80"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="106" t="s">
         <v>325</v>
       </c>
       <c r="B8" s="72" t="s">
@@ -6276,7 +6272,7 @@
       <c r="J8" s="76"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="130" t="s">
+      <c r="A9" s="110" t="s">
         <v>326</v>
       </c>
       <c r="B9" s="72" t="s">
@@ -6285,7 +6281,7 @@
       <c r="C9" s="72" t="s">
         <v>415</v>
       </c>
-      <c r="D9" s="123" cm="1">
+      <c r="D9" s="103" cm="1">
         <f t="array" aca="1" ref="D9" ca="1">IF(OR(IF(OR(A9="", B9="", C9=""), "", INDIRECT("'" &amp; B9 &amp; "'!" &amp; C9))=0, IF(OR(A9="", B9="", C9=""), "", INDIRECT("'" &amp; B9 &amp; "'!" &amp; C9))=""),"",INDIRECT("'" &amp; B9 &amp; "'!" &amp; C9))</f>
         <v>2.0736944174645666E-2</v>
       </c>
@@ -6295,16 +6291,16 @@
       <c r="J9" s="80"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="127" t="s">
+      <c r="A10" s="107" t="s">
         <v>327</v>
       </c>
-      <c r="B10" s="124" t="s">
+      <c r="B10" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C10" s="125" t="s">
+      <c r="C10" s="105" t="s">
         <v>416</v>
       </c>
-      <c r="D10" s="123" t="str" cm="1">
+      <c r="D10" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D10" ca="1">IF(OR(IF(OR(A10="", B10="", C10=""), "", INDIRECT("'" &amp; B10 &amp; "'!" &amp; C10))=0, IF(OR(A10="", B10="", C10=""), "", INDIRECT("'" &amp; B10 &amp; "'!" &amp; C10))=""),"",INDIRECT("'" &amp; B10 &amp; "'!" &amp; C10))</f>
         <v/>
       </c>
@@ -6314,16 +6310,16 @@
       <c r="J10" s="76"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="131" t="s">
+      <c r="A11" s="111" t="s">
         <v>328</v>
       </c>
-      <c r="B11" s="124" t="s">
+      <c r="B11" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C11" s="125" t="s">
+      <c r="C11" s="105" t="s">
         <v>417</v>
       </c>
-      <c r="D11" s="123" cm="1">
+      <c r="D11" s="103" cm="1">
         <f t="array" aca="1" ref="D11" ca="1">IF(OR(IF(OR(A11="", B11="", C11=""), "", INDIRECT("'" &amp; B11 &amp; "'!" &amp; C11))=0, IF(OR(A11="", B11="", C11=""), "", INDIRECT("'" &amp; B11 &amp; "'!" &amp; C11))=""),"",INDIRECT("'" &amp; B11 &amp; "'!" &amp; C11))</f>
         <v>3.5117348400309334E-2</v>
       </c>
@@ -6333,16 +6329,16 @@
       <c r="J11" s="80"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="127" t="s">
+      <c r="A12" s="107" t="s">
         <v>329</v>
       </c>
-      <c r="B12" s="124" t="s">
+      <c r="B12" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C12" s="125" t="s">
+      <c r="C12" s="105" t="s">
         <v>418</v>
       </c>
-      <c r="D12" s="123" t="str" cm="1">
+      <c r="D12" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D12" ca="1">IF(OR(IF(OR(A12="", B12="", C12=""), "", INDIRECT("'" &amp; B12 &amp; "'!" &amp; C12))=0, IF(OR(A12="", B12="", C12=""), "", INDIRECT("'" &amp; B12 &amp; "'!" &amp; C12))=""),"",INDIRECT("'" &amp; B12 &amp; "'!" &amp; C12))</f>
         <v/>
       </c>
@@ -6352,16 +6348,16 @@
       <c r="J12" s="76"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="131" t="s">
+      <c r="A13" s="111" t="s">
         <v>330</v>
       </c>
-      <c r="B13" s="124" t="s">
+      <c r="B13" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C13" s="125" t="s">
+      <c r="C13" s="105" t="s">
         <v>419</v>
       </c>
-      <c r="D13" s="123" cm="1">
+      <c r="D13" s="103" cm="1">
         <f t="array" aca="1" ref="D13" ca="1">IF(OR(IF(OR(A13="", B13="", C13=""), "", INDIRECT("'" &amp; B13 &amp; "'!" &amp; C13))=0, IF(OR(A13="", B13="", C13=""), "", INDIRECT("'" &amp; B13 &amp; "'!" &amp; C13))=""),"",INDIRECT("'" &amp; B13 &amp; "'!" &amp; C13))</f>
         <v>2.9548225004298212E-2</v>
       </c>
@@ -6371,16 +6367,16 @@
       <c r="J13" s="80"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="128" t="s">
+      <c r="A14" s="108" t="s">
         <v>331</v>
       </c>
-      <c r="B14" s="124" t="s">
+      <c r="B14" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C14" s="125" t="s">
+      <c r="C14" s="105" t="s">
         <v>420</v>
       </c>
-      <c r="D14" s="123" t="str" cm="1">
+      <c r="D14" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D14" ca="1">IF(OR(IF(OR(A14="", B14="", C14=""), "", INDIRECT("'" &amp; B14 &amp; "'!" &amp; C14))=0, IF(OR(A14="", B14="", C14=""), "", INDIRECT("'" &amp; B14 &amp; "'!" &amp; C14))=""),"",INDIRECT("'" &amp; B14 &amp; "'!" &amp; C14))</f>
         <v/>
       </c>
@@ -6390,16 +6386,16 @@
       <c r="J14" s="76"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="131" t="s">
+      <c r="A15" s="111" t="s">
         <v>332</v>
       </c>
-      <c r="B15" s="124" t="s">
+      <c r="B15" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C15" s="125" t="s">
+      <c r="C15" s="105" t="s">
         <v>421</v>
       </c>
-      <c r="D15" s="123" cm="1">
+      <c r="D15" s="103" cm="1">
         <f t="array" aca="1" ref="D15" ca="1">IF(OR(IF(OR(A15="", B15="", C15=""), "", INDIRECT("'" &amp; B15 &amp; "'!" &amp; C15))=0, IF(OR(A15="", B15="", C15=""), "", INDIRECT("'" &amp; B15 &amp; "'!" &amp; C15))=""),"",INDIRECT("'" &amp; B15 &amp; "'!" &amp; C15))</f>
         <v>6.3201478284775625E-3</v>
       </c>
@@ -6409,16 +6405,16 @@
       <c r="J15" s="80"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="128" t="s">
+      <c r="A16" s="108" t="s">
         <v>333</v>
       </c>
-      <c r="B16" s="124" t="s">
+      <c r="B16" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C16" s="125" t="s">
+      <c r="C16" s="105" t="s">
         <v>422</v>
       </c>
-      <c r="D16" s="123" t="str" cm="1">
+      <c r="D16" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D16" ca="1">IF(OR(IF(OR(A16="", B16="", C16=""), "", INDIRECT("'" &amp; B16 &amp; "'!" &amp; C16))=0, IF(OR(A16="", B16="", C16=""), "", INDIRECT("'" &amp; B16 &amp; "'!" &amp; C16))=""),"",INDIRECT("'" &amp; B16 &amp; "'!" &amp; C16))</f>
         <v/>
       </c>
@@ -6428,16 +6424,16 @@
       <c r="J16" s="76"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="131" t="s">
+      <c r="A17" s="111" t="s">
         <v>334</v>
       </c>
-      <c r="B17" s="124" t="s">
+      <c r="B17" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C17" s="125" t="s">
+      <c r="C17" s="105" t="s">
         <v>423</v>
       </c>
-      <c r="D17" s="123" cm="1">
+      <c r="D17" s="103" cm="1">
         <f t="array" aca="1" ref="D17" ca="1">IF(OR(IF(OR(A17="", B17="", C17=""), "", INDIRECT("'" &amp; B17 &amp; "'!" &amp; C17))=0, IF(OR(A17="", B17="", C17=""), "", INDIRECT("'" &amp; B17 &amp; "'!" &amp; C17))=""),"",INDIRECT("'" &amp; B17 &amp; "'!" &amp; C17))</f>
         <v>2.5219757035239265E-2</v>
       </c>
@@ -6447,16 +6443,16 @@
       <c r="J17" s="80"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="128" t="s">
+      <c r="A18" s="108" t="s">
         <v>335</v>
       </c>
-      <c r="B18" s="124" t="s">
+      <c r="B18" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C18" s="125" t="s">
+      <c r="C18" s="105" t="s">
         <v>424</v>
       </c>
-      <c r="D18" s="123" t="str" cm="1">
+      <c r="D18" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D18" ca="1">IF(OR(IF(OR(A18="", B18="", C18=""), "", INDIRECT("'" &amp; B18 &amp; "'!" &amp; C18))=0, IF(OR(A18="", B18="", C18=""), "", INDIRECT("'" &amp; B18 &amp; "'!" &amp; C18))=""),"",INDIRECT("'" &amp; B18 &amp; "'!" &amp; C18))</f>
         <v/>
       </c>
@@ -6466,16 +6462,16 @@
       <c r="J18" s="76"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="131" t="s">
+      <c r="A19" s="111" t="s">
         <v>336</v>
       </c>
-      <c r="B19" s="124" t="s">
+      <c r="B19" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C19" s="125" t="s">
+      <c r="C19" s="105" t="s">
         <v>425</v>
       </c>
-      <c r="D19" s="123" cm="1">
+      <c r="D19" s="103" cm="1">
         <f t="array" aca="1" ref="D19" ca="1">IF(OR(IF(OR(A19="", B19="", C19=""), "", INDIRECT("'" &amp; B19 &amp; "'!" &amp; C19))=0, IF(OR(A19="", B19="", C19=""), "", INDIRECT("'" &amp; B19 &amp; "'!" &amp; C19))=""),"",INDIRECT("'" &amp; B19 &amp; "'!" &amp; C19))</f>
         <v>5.2913605158896315E-2</v>
       </c>
@@ -6485,16 +6481,16 @@
       <c r="J19" s="80"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="128" t="s">
+      <c r="A20" s="108" t="s">
         <v>337</v>
       </c>
-      <c r="B20" s="124" t="s">
+      <c r="B20" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C20" s="125" t="s">
+      <c r="C20" s="105" t="s">
         <v>426</v>
       </c>
-      <c r="D20" s="123" t="str" cm="1">
+      <c r="D20" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D20" ca="1">IF(OR(IF(OR(A20="", B20="", C20=""), "", INDIRECT("'" &amp; B20 &amp; "'!" &amp; C20))=0, IF(OR(A20="", B20="", C20=""), "", INDIRECT("'" &amp; B20 &amp; "'!" &amp; C20))=""),"",INDIRECT("'" &amp; B20 &amp; "'!" &amp; C20))</f>
         <v/>
       </c>
@@ -6504,16 +6500,16 @@
       <c r="J20" s="76"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="131" t="s">
+      <c r="A21" s="111" t="s">
         <v>338</v>
       </c>
-      <c r="B21" s="124" t="s">
+      <c r="B21" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C21" s="125" t="s">
+      <c r="C21" s="105" t="s">
         <v>427</v>
       </c>
-      <c r="D21" s="123" cm="1">
+      <c r="D21" s="103" cm="1">
         <f t="array" aca="1" ref="D21" ca="1">IF(OR(IF(OR(A21="", B21="", C21=""), "", INDIRECT("'" &amp; B21 &amp; "'!" &amp; C21))=0, IF(OR(A21="", B21="", C21=""), "", INDIRECT("'" &amp; B21 &amp; "'!" &amp; C21))=""),"",INDIRECT("'" &amp; B21 &amp; "'!" &amp; C21))</f>
         <v>5.2018836646548605E-2</v>
       </c>
@@ -6523,16 +6519,16 @@
       <c r="J21" s="80"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="128" t="s">
+      <c r="A22" s="108" t="s">
         <v>339</v>
       </c>
-      <c r="B22" s="124" t="s">
+      <c r="B22" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C22" s="125" t="s">
+      <c r="C22" s="105" t="s">
         <v>428</v>
       </c>
-      <c r="D22" s="123" t="str" cm="1">
+      <c r="D22" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D22" ca="1">IF(OR(IF(OR(A22="", B22="", C22=""), "", INDIRECT("'" &amp; B22 &amp; "'!" &amp; C22))=0, IF(OR(A22="", B22="", C22=""), "", INDIRECT("'" &amp; B22 &amp; "'!" &amp; C22))=""),"",INDIRECT("'" &amp; B22 &amp; "'!" &amp; C22))</f>
         <v/>
       </c>
@@ -6542,16 +6538,16 @@
       <c r="J22" s="76"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="131" t="s">
+      <c r="A23" s="111" t="s">
         <v>340</v>
       </c>
-      <c r="B23" s="124" t="s">
+      <c r="B23" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="C23" s="125" t="s">
+      <c r="C23" s="105" t="s">
         <v>429</v>
       </c>
-      <c r="D23" s="123" cm="1">
+      <c r="D23" s="103" cm="1">
         <f t="array" aca="1" ref="D23" ca="1">IF(OR(IF(OR(A23="", B23="", C23=""), "", INDIRECT("'" &amp; B23 &amp; "'!" &amp; C23))=0, IF(OR(A23="", B23="", C23=""), "", INDIRECT("'" &amp; B23 &amp; "'!" &amp; C23))=""),"",INDIRECT("'" &amp; B23 &amp; "'!" &amp; C23))</f>
         <v>5.2900906226266198E-2</v>
       </c>
@@ -6561,7 +6557,7 @@
       <c r="J23" s="80"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="129" t="s">
+      <c r="A24" s="109" t="s">
         <v>341</v>
       </c>
       <c r="B24" s="65" t="s">
@@ -6580,7 +6576,7 @@
       <c r="J24" s="76"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="130" t="s">
+      <c r="A25" s="110" t="s">
         <v>342</v>
       </c>
       <c r="B25" s="72" t="s">
@@ -6599,7 +6595,7 @@
       <c r="J25" s="80"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="126" t="s">
+      <c r="A26" s="106" t="s">
         <v>343</v>
       </c>
       <c r="B26" s="72" t="s">
@@ -7763,22 +7759,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:G2 A6:G114">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>OR($C2=0, $A2="Header")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:G6">
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>$A2=Header</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:XFD32">
-    <cfRule type="expression" dxfId="11" priority="18">
+    <cfRule type="expression" dxfId="7" priority="18">
       <formula>#REF!=Header</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33:XFD33">
-    <cfRule type="expression" dxfId="10" priority="17">
+    <cfRule type="expression" dxfId="6" priority="17">
       <formula>$A6=Header</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10127,26 +10123,26 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="I1:L1 B1:G6 E8:G25 D8:D26">
-    <cfRule type="expression" dxfId="9" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$C1=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="6">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>$C1=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:L18">
-    <cfRule type="expression" dxfId="7" priority="11">
+    <cfRule type="expression" dxfId="3" priority="11">
       <formula>#REF!=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="12">
+    <cfRule type="expression" dxfId="2" priority="12">
       <formula>#REF!=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19:L19">
-    <cfRule type="expression" dxfId="5" priority="9">
+    <cfRule type="expression" dxfId="1" priority="9">
       <formula>$C6=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="10">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>$C6=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12276,10 +12272,10 @@
       <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="122" t="s">
+      <c r="F1" s="102" t="s">
         <v>411</v>
       </c>
-      <c r="G1" s="122" t="s">
+      <c r="G1" s="102" t="s">
         <v>412</v>
       </c>
     </row>
@@ -12293,8 +12289,8 @@
       <c r="C2" s="40" t="s">
         <v>266</v>
       </c>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -12306,8 +12302,8 @@
       <c r="C3" s="40" t="s">
         <v>267</v>
       </c>
-      <c r="F3" s="133"/>
-      <c r="G3" s="132"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="112"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -12319,8 +12315,8 @@
       <c r="C4" s="40" t="s">
         <v>268</v>
       </c>
-      <c r="F4" s="133"/>
-      <c r="G4" s="132"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="112"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -12332,8 +12328,8 @@
       <c r="C5" s="40" t="s">
         <v>269</v>
       </c>
-      <c r="F5" s="133"/>
-      <c r="G5" s="132"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="112"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -12345,8 +12341,8 @@
       <c r="C6" s="40" t="s">
         <v>270</v>
       </c>
-      <c r="F6" s="133"/>
-      <c r="G6" s="132"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="112"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -12358,8 +12354,8 @@
       <c r="C7" s="40" t="s">
         <v>271</v>
       </c>
-      <c r="F7" s="133"/>
-      <c r="G7" s="132"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="112"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -12371,8 +12367,8 @@
       <c r="C8" s="40" t="s">
         <v>272</v>
       </c>
-      <c r="F8" s="133"/>
-      <c r="G8" s="132"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="112"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -12384,8 +12380,8 @@
       <c r="C9" s="40" t="s">
         <v>273</v>
       </c>
-      <c r="F9" s="133"/>
-      <c r="G9" s="132"/>
+      <c r="F9" s="113"/>
+      <c r="G9" s="112"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -12397,8 +12393,8 @@
       <c r="C10" s="40" t="s">
         <v>274</v>
       </c>
-      <c r="F10" s="133"/>
-      <c r="G10" s="132"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="112"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -12410,8 +12406,8 @@
       <c r="C11" s="40" t="s">
         <v>275</v>
       </c>
-      <c r="F11" s="133"/>
-      <c r="G11" s="132"/>
+      <c r="F11" s="113"/>
+      <c r="G11" s="112"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -12423,8 +12419,8 @@
       <c r="C12" s="40" t="s">
         <v>276</v>
       </c>
-      <c r="F12" s="133"/>
-      <c r="G12" s="132"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="112"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -12436,8 +12432,8 @@
       <c r="C13" s="40" t="s">
         <v>277</v>
       </c>
-      <c r="F13" s="133"/>
-      <c r="G13" s="132"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="112"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -12449,8 +12445,8 @@
       <c r="C14" s="40" t="s">
         <v>278</v>
       </c>
-      <c r="F14" s="133"/>
-      <c r="G14" s="132"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="112"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -12462,8 +12458,8 @@
       <c r="C15" s="40" t="s">
         <v>279</v>
       </c>
-      <c r="F15" s="133"/>
-      <c r="G15" s="132"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="112"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -12475,8 +12471,8 @@
       <c r="C16" s="40" t="s">
         <v>280</v>
       </c>
-      <c r="F16" s="133"/>
-      <c r="G16" s="132"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="112"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -12488,8 +12484,8 @@
       <c r="C17" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="F17" s="133"/>
-      <c r="G17" s="132"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="112"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -12501,8 +12497,8 @@
       <c r="C18" s="40" t="s">
         <v>282</v>
       </c>
-      <c r="F18" s="133"/>
-      <c r="G18" s="132"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="112"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -12514,8 +12510,8 @@
       <c r="C19" s="40" t="s">
         <v>283</v>
       </c>
-      <c r="F19" s="133"/>
-      <c r="G19" s="132"/>
+      <c r="F19" s="113"/>
+      <c r="G19" s="112"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -12527,8 +12523,8 @@
       <c r="C20" s="40" t="s">
         <v>284</v>
       </c>
-      <c r="F20" s="133"/>
-      <c r="G20" s="132"/>
+      <c r="F20" s="113"/>
+      <c r="G20" s="112"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -12540,8 +12536,8 @@
       <c r="C21" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="F21" s="133"/>
-      <c r="G21" s="132"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="112"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -12553,8 +12549,8 @@
       <c r="C22" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="F22" s="133"/>
-      <c r="G22" s="132"/>
+      <c r="F22" s="113"/>
+      <c r="G22" s="112"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -12566,8 +12562,8 @@
       <c r="C23" s="40" t="s">
         <v>287</v>
       </c>
-      <c r="F23" s="133"/>
-      <c r="G23" s="132"/>
+      <c r="F23" s="113"/>
+      <c r="G23" s="112"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -12579,8 +12575,8 @@
       <c r="C24" s="40" t="s">
         <v>288</v>
       </c>
-      <c r="F24" s="133"/>
-      <c r="G24" s="132"/>
+      <c r="F24" s="113"/>
+      <c r="G24" s="112"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -12592,8 +12588,8 @@
       <c r="C25" s="40" t="s">
         <v>289</v>
       </c>
-      <c r="F25" s="133"/>
-      <c r="G25" s="132"/>
+      <c r="F25" s="113"/>
+      <c r="G25" s="112"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -12605,8 +12601,8 @@
       <c r="C26" s="40" t="s">
         <v>290</v>
       </c>
-      <c r="F26" s="133"/>
-      <c r="G26" s="132"/>
+      <c r="F26" s="113"/>
+      <c r="G26" s="112"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -12618,8 +12614,8 @@
       <c r="C27" s="40" t="s">
         <v>291</v>
       </c>
-      <c r="F27" s="133"/>
-      <c r="G27" s="132"/>
+      <c r="F27" s="113"/>
+      <c r="G27" s="112"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -12631,8 +12627,8 @@
       <c r="C28" s="40" t="s">
         <v>292</v>
       </c>
-      <c r="F28" s="133"/>
-      <c r="G28" s="132"/>
+      <c r="F28" s="113"/>
+      <c r="G28" s="112"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -12644,8 +12640,8 @@
       <c r="C29" s="40" t="s">
         <v>293</v>
       </c>
-      <c r="F29" s="133"/>
-      <c r="G29" s="132"/>
+      <c r="F29" s="113"/>
+      <c r="G29" s="112"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -12657,8 +12653,8 @@
       <c r="C30" s="40" t="s">
         <v>294</v>
       </c>
-      <c r="F30" s="133"/>
-      <c r="G30" s="132"/>
+      <c r="F30" s="113"/>
+      <c r="G30" s="112"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -12670,12 +12666,12 @@
       <c r="C31" s="40" t="s">
         <v>295</v>
       </c>
-      <c r="F31" s="133"/>
-      <c r="G31" s="132"/>
+      <c r="F31" s="113"/>
+      <c r="G31" s="112"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F32" s="133"/>
-      <c r="G32" s="134"/>
+      <c r="F32" s="113"/>
+      <c r="G32" s="114"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15368,10 +15364,10 @@
       </c>
     </row>
     <row r="91" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J91" s="98" t="s">
+      <c r="J91" s="122" t="s">
         <v>31</v>
       </c>
-      <c r="K91" s="98"/>
+      <c r="K91" s="122"/>
     </row>
     <row r="92" spans="10:11" ht="49.5" x14ac:dyDescent="0.25">
       <c r="J92" s="10" t="s">
@@ -17070,14 +17066,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:160" x14ac:dyDescent="0.25">
-      <c r="B1" s="108" t="s">
+      <c r="B1" s="125" t="s">
         <v>223</v>
       </c>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
       <c r="H1" s="49"/>
       <c r="I1" s="49"/>
       <c r="J1" s="49"/>
@@ -17087,14 +17083,14 @@
       <c r="N1" s="49"/>
       <c r="O1" s="49"/>
       <c r="P1" s="49"/>
-      <c r="R1" s="111" t="s">
+      <c r="R1" s="128" t="s">
         <v>223</v>
       </c>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
+      <c r="W1" s="129"/>
       <c r="X1" s="34"/>
       <c r="Y1" s="34"/>
       <c r="Z1" s="34"/>
@@ -17104,14 +17100,14 @@
       <c r="AD1" s="34"/>
       <c r="AE1" s="34"/>
       <c r="AF1" s="34"/>
-      <c r="AH1" s="108" t="s">
+      <c r="AH1" s="125" t="s">
         <v>223</v>
       </c>
-      <c r="AI1" s="107"/>
-      <c r="AJ1" s="107"/>
-      <c r="AK1" s="107"/>
-      <c r="AL1" s="107"/>
-      <c r="AM1" s="107"/>
+      <c r="AI1" s="124"/>
+      <c r="AJ1" s="124"/>
+      <c r="AK1" s="124"/>
+      <c r="AL1" s="124"/>
+      <c r="AM1" s="124"/>
       <c r="AN1" s="49"/>
       <c r="AO1" s="49"/>
       <c r="AP1" s="49"/>
@@ -17121,14 +17117,14 @@
       <c r="AT1" s="49"/>
       <c r="AU1" s="49"/>
       <c r="AV1" s="49"/>
-      <c r="AX1" s="108" t="s">
+      <c r="AX1" s="125" t="s">
         <v>223</v>
       </c>
-      <c r="AY1" s="107"/>
-      <c r="AZ1" s="107"/>
-      <c r="BA1" s="107"/>
-      <c r="BB1" s="107"/>
-      <c r="BC1" s="107"/>
+      <c r="AY1" s="124"/>
+      <c r="AZ1" s="124"/>
+      <c r="BA1" s="124"/>
+      <c r="BB1" s="124"/>
+      <c r="BC1" s="124"/>
       <c r="BD1" s="49"/>
       <c r="BE1" s="49"/>
       <c r="BF1" s="49"/>
@@ -17138,14 +17134,14 @@
       <c r="BJ1" s="49"/>
       <c r="BK1" s="49"/>
       <c r="BL1" s="49"/>
-      <c r="BN1" s="108" t="s">
+      <c r="BN1" s="125" t="s">
         <v>223</v>
       </c>
-      <c r="BO1" s="107"/>
-      <c r="BP1" s="107"/>
-      <c r="BQ1" s="107"/>
-      <c r="BR1" s="107"/>
-      <c r="BS1" s="107"/>
+      <c r="BO1" s="124"/>
+      <c r="BP1" s="124"/>
+      <c r="BQ1" s="124"/>
+      <c r="BR1" s="124"/>
+      <c r="BS1" s="124"/>
       <c r="BT1" s="49"/>
       <c r="BU1" s="49"/>
       <c r="BV1" s="49"/>
@@ -17156,14 +17152,14 @@
       <c r="CA1" s="49"/>
       <c r="CB1" s="49"/>
       <c r="CC1" s="34"/>
-      <c r="CD1" s="108" t="s">
+      <c r="CD1" s="125" t="s">
         <v>223</v>
       </c>
-      <c r="CE1" s="107"/>
-      <c r="CF1" s="107"/>
-      <c r="CG1" s="107"/>
-      <c r="CH1" s="107"/>
-      <c r="CI1" s="107"/>
+      <c r="CE1" s="124"/>
+      <c r="CF1" s="124"/>
+      <c r="CG1" s="124"/>
+      <c r="CH1" s="124"/>
+      <c r="CI1" s="124"/>
       <c r="CJ1" s="49"/>
       <c r="CK1" s="49"/>
       <c r="CL1" s="49"/>
@@ -17173,14 +17169,14 @@
       <c r="CP1" s="49"/>
       <c r="CQ1" s="49"/>
       <c r="CR1" s="49"/>
-      <c r="CT1" s="108" t="s">
+      <c r="CT1" s="125" t="s">
         <v>223</v>
       </c>
-      <c r="CU1" s="107"/>
-      <c r="CV1" s="107"/>
-      <c r="CW1" s="107"/>
-      <c r="CX1" s="107"/>
-      <c r="CY1" s="107"/>
+      <c r="CU1" s="124"/>
+      <c r="CV1" s="124"/>
+      <c r="CW1" s="124"/>
+      <c r="CX1" s="124"/>
+      <c r="CY1" s="124"/>
       <c r="CZ1" s="49"/>
       <c r="DA1" s="49"/>
       <c r="DB1" s="49"/>
@@ -17190,14 +17186,14 @@
       <c r="DF1" s="49"/>
       <c r="DG1" s="49"/>
       <c r="DH1" s="49"/>
-      <c r="DJ1" s="108" t="s">
+      <c r="DJ1" s="125" t="s">
         <v>223</v>
       </c>
-      <c r="DK1" s="107"/>
-      <c r="DL1" s="107"/>
-      <c r="DM1" s="107"/>
-      <c r="DN1" s="107"/>
-      <c r="DO1" s="107"/>
+      <c r="DK1" s="124"/>
+      <c r="DL1" s="124"/>
+      <c r="DM1" s="124"/>
+      <c r="DN1" s="124"/>
+      <c r="DO1" s="124"/>
       <c r="DP1" s="49"/>
       <c r="DQ1" s="49"/>
       <c r="DR1" s="49"/>
@@ -17207,14 +17203,14 @@
       <c r="DV1" s="49"/>
       <c r="DW1" s="49"/>
       <c r="DX1" s="49"/>
-      <c r="DZ1" s="108" t="s">
+      <c r="DZ1" s="125" t="s">
         <v>223</v>
       </c>
-      <c r="EA1" s="107"/>
-      <c r="EB1" s="107"/>
-      <c r="EC1" s="107"/>
-      <c r="ED1" s="107"/>
-      <c r="EE1" s="107"/>
+      <c r="EA1" s="124"/>
+      <c r="EB1" s="124"/>
+      <c r="EC1" s="124"/>
+      <c r="ED1" s="124"/>
+      <c r="EE1" s="124"/>
       <c r="EF1" s="49"/>
       <c r="EG1" s="49"/>
       <c r="EH1" s="49"/>
@@ -17224,14 +17220,14 @@
       <c r="EL1" s="49"/>
       <c r="EM1" s="49"/>
       <c r="EN1" s="49"/>
-      <c r="EP1" s="108" t="s">
+      <c r="EP1" s="125" t="s">
         <v>223</v>
       </c>
-      <c r="EQ1" s="107"/>
-      <c r="ER1" s="107"/>
-      <c r="ES1" s="107"/>
-      <c r="ET1" s="107"/>
-      <c r="EU1" s="107"/>
+      <c r="EQ1" s="124"/>
+      <c r="ER1" s="124"/>
+      <c r="ES1" s="124"/>
+      <c r="ET1" s="124"/>
+      <c r="EU1" s="124"/>
       <c r="EV1" s="49"/>
       <c r="EW1" s="49"/>
       <c r="EX1" s="49"/>
@@ -17243,14 +17239,14 @@
       <c r="FD1" s="49"/>
     </row>
     <row r="2" spans="2:160" x14ac:dyDescent="0.25">
-      <c r="B2" s="108" t="s">
+      <c r="B2" s="125" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
       <c r="H2" s="49"/>
       <c r="I2" s="49"/>
       <c r="J2" s="49"/>
@@ -17260,14 +17256,14 @@
       <c r="N2" s="49"/>
       <c r="O2" s="49"/>
       <c r="P2" s="49"/>
-      <c r="R2" s="111" t="s">
+      <c r="R2" s="128" t="s">
         <v>224</v>
       </c>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
-      <c r="U2" s="112"/>
-      <c r="V2" s="112"/>
-      <c r="W2" s="112"/>
+      <c r="S2" s="129"/>
+      <c r="T2" s="129"/>
+      <c r="U2" s="129"/>
+      <c r="V2" s="129"/>
+      <c r="W2" s="129"/>
       <c r="X2" s="34"/>
       <c r="Y2" s="34"/>
       <c r="Z2" s="34"/>
@@ -17277,14 +17273,14 @@
       <c r="AD2" s="34"/>
       <c r="AE2" s="34"/>
       <c r="AF2" s="34"/>
-      <c r="AH2" s="108" t="s">
+      <c r="AH2" s="125" t="s">
         <v>224</v>
       </c>
-      <c r="AI2" s="107"/>
-      <c r="AJ2" s="107"/>
-      <c r="AK2" s="107"/>
-      <c r="AL2" s="107"/>
-      <c r="AM2" s="107"/>
+      <c r="AI2" s="124"/>
+      <c r="AJ2" s="124"/>
+      <c r="AK2" s="124"/>
+      <c r="AL2" s="124"/>
+      <c r="AM2" s="124"/>
       <c r="AN2" s="49"/>
       <c r="AO2" s="49"/>
       <c r="AP2" s="49"/>
@@ -17294,14 +17290,14 @@
       <c r="AT2" s="49"/>
       <c r="AU2" s="49"/>
       <c r="AV2" s="49"/>
-      <c r="AX2" s="108" t="s">
+      <c r="AX2" s="125" t="s">
         <v>224</v>
       </c>
-      <c r="AY2" s="107"/>
-      <c r="AZ2" s="107"/>
-      <c r="BA2" s="107"/>
-      <c r="BB2" s="107"/>
-      <c r="BC2" s="107"/>
+      <c r="AY2" s="124"/>
+      <c r="AZ2" s="124"/>
+      <c r="BA2" s="124"/>
+      <c r="BB2" s="124"/>
+      <c r="BC2" s="124"/>
       <c r="BD2" s="49"/>
       <c r="BE2" s="49"/>
       <c r="BF2" s="49"/>
@@ -17311,14 +17307,14 @@
       <c r="BJ2" s="49"/>
       <c r="BK2" s="49"/>
       <c r="BL2" s="49"/>
-      <c r="BN2" s="108" t="s">
+      <c r="BN2" s="125" t="s">
         <v>224</v>
       </c>
-      <c r="BO2" s="107"/>
-      <c r="BP2" s="107"/>
-      <c r="BQ2" s="107"/>
-      <c r="BR2" s="107"/>
-      <c r="BS2" s="107"/>
+      <c r="BO2" s="124"/>
+      <c r="BP2" s="124"/>
+      <c r="BQ2" s="124"/>
+      <c r="BR2" s="124"/>
+      <c r="BS2" s="124"/>
       <c r="BT2" s="49"/>
       <c r="BU2" s="49"/>
       <c r="BV2" s="49"/>
@@ -17329,14 +17325,14 @@
       <c r="CA2" s="49"/>
       <c r="CB2" s="49"/>
       <c r="CC2" s="34"/>
-      <c r="CD2" s="108" t="s">
+      <c r="CD2" s="125" t="s">
         <v>224</v>
       </c>
-      <c r="CE2" s="107"/>
-      <c r="CF2" s="107"/>
-      <c r="CG2" s="107"/>
-      <c r="CH2" s="107"/>
-      <c r="CI2" s="107"/>
+      <c r="CE2" s="124"/>
+      <c r="CF2" s="124"/>
+      <c r="CG2" s="124"/>
+      <c r="CH2" s="124"/>
+      <c r="CI2" s="124"/>
       <c r="CJ2" s="49"/>
       <c r="CK2" s="49"/>
       <c r="CL2" s="49"/>
@@ -17346,14 +17342,14 @@
       <c r="CP2" s="49"/>
       <c r="CQ2" s="49"/>
       <c r="CR2" s="49"/>
-      <c r="CT2" s="108" t="s">
+      <c r="CT2" s="125" t="s">
         <v>224</v>
       </c>
-      <c r="CU2" s="107"/>
-      <c r="CV2" s="107"/>
-      <c r="CW2" s="107"/>
-      <c r="CX2" s="107"/>
-      <c r="CY2" s="107"/>
+      <c r="CU2" s="124"/>
+      <c r="CV2" s="124"/>
+      <c r="CW2" s="124"/>
+      <c r="CX2" s="124"/>
+      <c r="CY2" s="124"/>
       <c r="CZ2" s="49"/>
       <c r="DA2" s="49"/>
       <c r="DB2" s="49"/>
@@ -17363,14 +17359,14 @@
       <c r="DF2" s="49"/>
       <c r="DG2" s="49"/>
       <c r="DH2" s="49"/>
-      <c r="DJ2" s="108" t="s">
+      <c r="DJ2" s="125" t="s">
         <v>224</v>
       </c>
-      <c r="DK2" s="107"/>
-      <c r="DL2" s="107"/>
-      <c r="DM2" s="107"/>
-      <c r="DN2" s="107"/>
-      <c r="DO2" s="107"/>
+      <c r="DK2" s="124"/>
+      <c r="DL2" s="124"/>
+      <c r="DM2" s="124"/>
+      <c r="DN2" s="124"/>
+      <c r="DO2" s="124"/>
       <c r="DP2" s="49"/>
       <c r="DQ2" s="49"/>
       <c r="DR2" s="49"/>
@@ -17380,14 +17376,14 @@
       <c r="DV2" s="49"/>
       <c r="DW2" s="49"/>
       <c r="DX2" s="49"/>
-      <c r="DZ2" s="108" t="s">
+      <c r="DZ2" s="125" t="s">
         <v>224</v>
       </c>
-      <c r="EA2" s="107"/>
-      <c r="EB2" s="107"/>
-      <c r="EC2" s="107"/>
-      <c r="ED2" s="107"/>
-      <c r="EE2" s="107"/>
+      <c r="EA2" s="124"/>
+      <c r="EB2" s="124"/>
+      <c r="EC2" s="124"/>
+      <c r="ED2" s="124"/>
+      <c r="EE2" s="124"/>
       <c r="EF2" s="49"/>
       <c r="EG2" s="49"/>
       <c r="EH2" s="49"/>
@@ -17397,14 +17393,14 @@
       <c r="EL2" s="49"/>
       <c r="EM2" s="49"/>
       <c r="EN2" s="49"/>
-      <c r="EP2" s="108" t="s">
+      <c r="EP2" s="125" t="s">
         <v>224</v>
       </c>
-      <c r="EQ2" s="107"/>
-      <c r="ER2" s="107"/>
-      <c r="ES2" s="107"/>
-      <c r="ET2" s="107"/>
-      <c r="EU2" s="107"/>
+      <c r="EQ2" s="124"/>
+      <c r="ER2" s="124"/>
+      <c r="ES2" s="124"/>
+      <c r="ET2" s="124"/>
+      <c r="EU2" s="124"/>
       <c r="EV2" s="49"/>
       <c r="EW2" s="49"/>
       <c r="EX2" s="49"/>
@@ -17416,12 +17412,12 @@
       <c r="FD2" s="49"/>
     </row>
     <row r="3" spans="2:160" x14ac:dyDescent="0.25">
-      <c r="B3" s="107"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
       <c r="H3" s="49"/>
       <c r="I3" s="49"/>
       <c r="J3" s="49"/>
@@ -17431,12 +17427,12 @@
       <c r="N3" s="49"/>
       <c r="O3" s="49"/>
       <c r="P3" s="49"/>
-      <c r="R3" s="112"/>
-      <c r="S3" s="112"/>
-      <c r="T3" s="112"/>
-      <c r="U3" s="112"/>
-      <c r="V3" s="112"/>
-      <c r="W3" s="112"/>
+      <c r="R3" s="129"/>
+      <c r="S3" s="129"/>
+      <c r="T3" s="129"/>
+      <c r="U3" s="129"/>
+      <c r="V3" s="129"/>
+      <c r="W3" s="129"/>
       <c r="X3" s="34"/>
       <c r="Y3" s="34"/>
       <c r="Z3" s="34"/>
@@ -17446,12 +17442,12 @@
       <c r="AD3" s="34"/>
       <c r="AE3" s="34"/>
       <c r="AF3" s="34"/>
-      <c r="AH3" s="107"/>
-      <c r="AI3" s="107"/>
-      <c r="AJ3" s="107"/>
-      <c r="AK3" s="107"/>
-      <c r="AL3" s="107"/>
-      <c r="AM3" s="107"/>
+      <c r="AH3" s="124"/>
+      <c r="AI3" s="124"/>
+      <c r="AJ3" s="124"/>
+      <c r="AK3" s="124"/>
+      <c r="AL3" s="124"/>
+      <c r="AM3" s="124"/>
       <c r="AN3" s="49"/>
       <c r="AO3" s="49"/>
       <c r="AP3" s="49"/>
@@ -17461,12 +17457,12 @@
       <c r="AT3" s="49"/>
       <c r="AU3" s="49"/>
       <c r="AV3" s="49"/>
-      <c r="AX3" s="107"/>
-      <c r="AY3" s="107"/>
-      <c r="AZ3" s="107"/>
-      <c r="BA3" s="107"/>
-      <c r="BB3" s="107"/>
-      <c r="BC3" s="107"/>
+      <c r="AX3" s="124"/>
+      <c r="AY3" s="124"/>
+      <c r="AZ3" s="124"/>
+      <c r="BA3" s="124"/>
+      <c r="BB3" s="124"/>
+      <c r="BC3" s="124"/>
       <c r="BD3" s="49"/>
       <c r="BE3" s="49"/>
       <c r="BF3" s="49"/>
@@ -17476,12 +17472,12 @@
       <c r="BJ3" s="49"/>
       <c r="BK3" s="49"/>
       <c r="BL3" s="49"/>
-      <c r="BN3" s="107"/>
-      <c r="BO3" s="107"/>
-      <c r="BP3" s="107"/>
-      <c r="BQ3" s="107"/>
-      <c r="BR3" s="107"/>
-      <c r="BS3" s="107"/>
+      <c r="BN3" s="124"/>
+      <c r="BO3" s="124"/>
+      <c r="BP3" s="124"/>
+      <c r="BQ3" s="124"/>
+      <c r="BR3" s="124"/>
+      <c r="BS3" s="124"/>
       <c r="BT3" s="49"/>
       <c r="BU3" s="49"/>
       <c r="BV3" s="49"/>
@@ -17492,12 +17488,12 @@
       <c r="CA3" s="49"/>
       <c r="CB3" s="49"/>
       <c r="CC3" s="34"/>
-      <c r="CD3" s="107"/>
-      <c r="CE3" s="107"/>
-      <c r="CF3" s="107"/>
-      <c r="CG3" s="107"/>
-      <c r="CH3" s="107"/>
-      <c r="CI3" s="107"/>
+      <c r="CD3" s="124"/>
+      <c r="CE3" s="124"/>
+      <c r="CF3" s="124"/>
+      <c r="CG3" s="124"/>
+      <c r="CH3" s="124"/>
+      <c r="CI3" s="124"/>
       <c r="CJ3" s="49"/>
       <c r="CK3" s="49"/>
       <c r="CL3" s="49"/>
@@ -17507,12 +17503,12 @@
       <c r="CP3" s="49"/>
       <c r="CQ3" s="49"/>
       <c r="CR3" s="49"/>
-      <c r="CT3" s="107"/>
-      <c r="CU3" s="107"/>
-      <c r="CV3" s="107"/>
-      <c r="CW3" s="107"/>
-      <c r="CX3" s="107"/>
-      <c r="CY3" s="107"/>
+      <c r="CT3" s="124"/>
+      <c r="CU3" s="124"/>
+      <c r="CV3" s="124"/>
+      <c r="CW3" s="124"/>
+      <c r="CX3" s="124"/>
+      <c r="CY3" s="124"/>
       <c r="CZ3" s="49"/>
       <c r="DA3" s="49"/>
       <c r="DB3" s="49"/>
@@ -17522,12 +17518,12 @@
       <c r="DF3" s="49"/>
       <c r="DG3" s="49"/>
       <c r="DH3" s="49"/>
-      <c r="DJ3" s="107"/>
-      <c r="DK3" s="107"/>
-      <c r="DL3" s="107"/>
-      <c r="DM3" s="107"/>
-      <c r="DN3" s="107"/>
-      <c r="DO3" s="107"/>
+      <c r="DJ3" s="124"/>
+      <c r="DK3" s="124"/>
+      <c r="DL3" s="124"/>
+      <c r="DM3" s="124"/>
+      <c r="DN3" s="124"/>
+      <c r="DO3" s="124"/>
       <c r="DP3" s="49"/>
       <c r="DQ3" s="49"/>
       <c r="DR3" s="49"/>
@@ -17537,12 +17533,12 @@
       <c r="DV3" s="49"/>
       <c r="DW3" s="49"/>
       <c r="DX3" s="49"/>
-      <c r="DZ3" s="107"/>
-      <c r="EA3" s="107"/>
-      <c r="EB3" s="107"/>
-      <c r="EC3" s="107"/>
-      <c r="ED3" s="107"/>
-      <c r="EE3" s="107"/>
+      <c r="DZ3" s="124"/>
+      <c r="EA3" s="124"/>
+      <c r="EB3" s="124"/>
+      <c r="EC3" s="124"/>
+      <c r="ED3" s="124"/>
+      <c r="EE3" s="124"/>
       <c r="EF3" s="49"/>
       <c r="EG3" s="49"/>
       <c r="EH3" s="49"/>
@@ -17552,12 +17548,12 @@
       <c r="EL3" s="49"/>
       <c r="EM3" s="49"/>
       <c r="EN3" s="49"/>
-      <c r="EP3" s="107"/>
-      <c r="EQ3" s="107"/>
-      <c r="ER3" s="107"/>
-      <c r="ES3" s="107"/>
-      <c r="ET3" s="107"/>
-      <c r="EU3" s="107"/>
+      <c r="EP3" s="124"/>
+      <c r="EQ3" s="124"/>
+      <c r="ER3" s="124"/>
+      <c r="ES3" s="124"/>
+      <c r="ET3" s="124"/>
+      <c r="EU3" s="124"/>
       <c r="EV3" s="49"/>
       <c r="EW3" s="49"/>
       <c r="EX3" s="49"/>
@@ -17572,13 +17568,13 @@
       <c r="B4" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="126" t="s">
         <v>170</v>
       </c>
-      <c r="D4" s="107"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="124"/>
       <c r="H4" s="49"/>
       <c r="I4" s="49"/>
       <c r="J4" s="49"/>
@@ -17591,13 +17587,13 @@
       <c r="R4" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="S4" s="114" t="s">
+      <c r="S4" s="131" t="s">
         <v>225</v>
       </c>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112"/>
+      <c r="T4" s="129"/>
+      <c r="U4" s="129"/>
+      <c r="V4" s="129"/>
+      <c r="W4" s="129"/>
       <c r="X4" s="34"/>
       <c r="Y4" s="34"/>
       <c r="Z4" s="34"/>
@@ -17610,13 +17606,13 @@
       <c r="AH4" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="AI4" s="109" t="s">
+      <c r="AI4" s="126" t="s">
         <v>147</v>
       </c>
-      <c r="AJ4" s="107"/>
-      <c r="AK4" s="107"/>
-      <c r="AL4" s="107"/>
-      <c r="AM4" s="107"/>
+      <c r="AJ4" s="124"/>
+      <c r="AK4" s="124"/>
+      <c r="AL4" s="124"/>
+      <c r="AM4" s="124"/>
       <c r="AN4" s="49"/>
       <c r="AO4" s="49"/>
       <c r="AP4" s="49"/>
@@ -17629,13 +17625,13 @@
       <c r="AX4" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="AY4" s="109" t="s">
+      <c r="AY4" s="126" t="s">
         <v>171</v>
       </c>
-      <c r="AZ4" s="107"/>
-      <c r="BA4" s="107"/>
-      <c r="BB4" s="107"/>
-      <c r="BC4" s="107"/>
+      <c r="AZ4" s="124"/>
+      <c r="BA4" s="124"/>
+      <c r="BB4" s="124"/>
+      <c r="BC4" s="124"/>
       <c r="BD4" s="49"/>
       <c r="BE4" s="49"/>
       <c r="BF4" s="49"/>
@@ -17648,13 +17644,13 @@
       <c r="BN4" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="BO4" s="109" t="s">
+      <c r="BO4" s="126" t="s">
         <v>244</v>
       </c>
-      <c r="BP4" s="107"/>
-      <c r="BQ4" s="107"/>
-      <c r="BR4" s="107"/>
-      <c r="BS4" s="107"/>
+      <c r="BP4" s="124"/>
+      <c r="BQ4" s="124"/>
+      <c r="BR4" s="124"/>
+      <c r="BS4" s="124"/>
       <c r="BT4" s="49"/>
       <c r="BU4" s="49"/>
       <c r="BV4" s="49"/>
@@ -17668,13 +17664,13 @@
       <c r="CD4" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="CE4" s="109" t="s">
+      <c r="CE4" s="126" t="s">
         <v>241</v>
       </c>
-      <c r="CF4" s="107"/>
-      <c r="CG4" s="107"/>
-      <c r="CH4" s="107"/>
-      <c r="CI4" s="107"/>
+      <c r="CF4" s="124"/>
+      <c r="CG4" s="124"/>
+      <c r="CH4" s="124"/>
+      <c r="CI4" s="124"/>
       <c r="CJ4" s="49"/>
       <c r="CK4" s="49"/>
       <c r="CL4" s="49"/>
@@ -17687,13 +17683,13 @@
       <c r="CT4" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="CU4" s="109" t="s">
+      <c r="CU4" s="126" t="s">
         <v>257</v>
       </c>
-      <c r="CV4" s="107"/>
-      <c r="CW4" s="107"/>
-      <c r="CX4" s="107"/>
-      <c r="CY4" s="107"/>
+      <c r="CV4" s="124"/>
+      <c r="CW4" s="124"/>
+      <c r="CX4" s="124"/>
+      <c r="CY4" s="124"/>
       <c r="CZ4" s="49"/>
       <c r="DA4" s="49"/>
       <c r="DB4" s="49"/>
@@ -17706,13 +17702,13 @@
       <c r="DJ4" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="DK4" s="109" t="s">
+      <c r="DK4" s="126" t="s">
         <v>231</v>
       </c>
-      <c r="DL4" s="107"/>
-      <c r="DM4" s="107"/>
-      <c r="DN4" s="107"/>
-      <c r="DO4" s="107"/>
+      <c r="DL4" s="124"/>
+      <c r="DM4" s="124"/>
+      <c r="DN4" s="124"/>
+      <c r="DO4" s="124"/>
       <c r="DP4" s="49"/>
       <c r="DQ4" s="49"/>
       <c r="DR4" s="49"/>
@@ -17725,13 +17721,13 @@
       <c r="DZ4" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="EA4" s="109" t="s">
+      <c r="EA4" s="126" t="s">
         <v>248</v>
       </c>
-      <c r="EB4" s="107"/>
-      <c r="EC4" s="107"/>
-      <c r="ED4" s="107"/>
-      <c r="EE4" s="107"/>
+      <c r="EB4" s="124"/>
+      <c r="EC4" s="124"/>
+      <c r="ED4" s="124"/>
+      <c r="EE4" s="124"/>
       <c r="EF4" s="49"/>
       <c r="EG4" s="49"/>
       <c r="EH4" s="49"/>
@@ -17744,13 +17740,13 @@
       <c r="EP4" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="EQ4" s="109" t="s">
+      <c r="EQ4" s="126" t="s">
         <v>236</v>
       </c>
-      <c r="ER4" s="107"/>
-      <c r="ES4" s="107"/>
-      <c r="ET4" s="107"/>
-      <c r="EU4" s="107"/>
+      <c r="ER4" s="124"/>
+      <c r="ES4" s="124"/>
+      <c r="ET4" s="124"/>
+      <c r="EU4" s="124"/>
       <c r="EV4" s="49"/>
       <c r="EW4" s="49"/>
       <c r="EX4" s="49"/>
@@ -17762,14 +17758,14 @@
       <c r="FD4" s="49"/>
     </row>
     <row r="5" spans="2:160" x14ac:dyDescent="0.25">
-      <c r="B5" s="110" t="s">
+      <c r="B5" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="107"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="124"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
       <c r="H5" s="49"/>
       <c r="I5" s="49"/>
       <c r="J5" s="49"/>
@@ -17779,14 +17775,14 @@
       <c r="N5" s="49"/>
       <c r="O5" s="49"/>
       <c r="P5" s="49"/>
-      <c r="R5" s="115" t="s">
+      <c r="R5" s="132" t="s">
         <v>31</v>
       </c>
-      <c r="S5" s="112"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="112"/>
-      <c r="V5" s="112"/>
-      <c r="W5" s="112"/>
+      <c r="S5" s="129"/>
+      <c r="T5" s="129"/>
+      <c r="U5" s="129"/>
+      <c r="V5" s="129"/>
+      <c r="W5" s="129"/>
       <c r="X5" s="34"/>
       <c r="Y5" s="34"/>
       <c r="Z5" s="34"/>
@@ -17796,14 +17792,14 @@
       <c r="AD5" s="34"/>
       <c r="AE5" s="34"/>
       <c r="AF5" s="34"/>
-      <c r="AH5" s="110" t="s">
+      <c r="AH5" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="AI5" s="107"/>
-      <c r="AJ5" s="107"/>
-      <c r="AK5" s="107"/>
-      <c r="AL5" s="107"/>
-      <c r="AM5" s="107"/>
+      <c r="AI5" s="124"/>
+      <c r="AJ5" s="124"/>
+      <c r="AK5" s="124"/>
+      <c r="AL5" s="124"/>
+      <c r="AM5" s="124"/>
       <c r="AN5" s="49"/>
       <c r="AO5" s="49"/>
       <c r="AP5" s="49"/>
@@ -17813,14 +17809,14 @@
       <c r="AT5" s="49"/>
       <c r="AU5" s="49"/>
       <c r="AV5" s="49"/>
-      <c r="AX5" s="110" t="s">
+      <c r="AX5" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="AY5" s="107"/>
-      <c r="AZ5" s="107"/>
-      <c r="BA5" s="107"/>
-      <c r="BB5" s="107"/>
-      <c r="BC5" s="107"/>
+      <c r="AY5" s="124"/>
+      <c r="AZ5" s="124"/>
+      <c r="BA5" s="124"/>
+      <c r="BB5" s="124"/>
+      <c r="BC5" s="124"/>
       <c r="BD5" s="49"/>
       <c r="BE5" s="49"/>
       <c r="BF5" s="49"/>
@@ -17830,14 +17826,14 @@
       <c r="BJ5" s="49"/>
       <c r="BK5" s="49"/>
       <c r="BL5" s="49"/>
-      <c r="BN5" s="110" t="s">
+      <c r="BN5" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="BO5" s="107"/>
-      <c r="BP5" s="107"/>
-      <c r="BQ5" s="107"/>
-      <c r="BR5" s="107"/>
-      <c r="BS5" s="107"/>
+      <c r="BO5" s="124"/>
+      <c r="BP5" s="124"/>
+      <c r="BQ5" s="124"/>
+      <c r="BR5" s="124"/>
+      <c r="BS5" s="124"/>
       <c r="BT5" s="49"/>
       <c r="BU5" s="49"/>
       <c r="BV5" s="49"/>
@@ -17848,14 +17844,14 @@
       <c r="CA5" s="49"/>
       <c r="CB5" s="49"/>
       <c r="CC5" s="34"/>
-      <c r="CD5" s="110" t="s">
+      <c r="CD5" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="CE5" s="107"/>
-      <c r="CF5" s="107"/>
-      <c r="CG5" s="107"/>
-      <c r="CH5" s="107"/>
-      <c r="CI5" s="107"/>
+      <c r="CE5" s="124"/>
+      <c r="CF5" s="124"/>
+      <c r="CG5" s="124"/>
+      <c r="CH5" s="124"/>
+      <c r="CI5" s="124"/>
       <c r="CJ5" s="49"/>
       <c r="CK5" s="49"/>
       <c r="CL5" s="49"/>
@@ -17865,14 +17861,14 @@
       <c r="CP5" s="49"/>
       <c r="CQ5" s="49"/>
       <c r="CR5" s="49"/>
-      <c r="CT5" s="110" t="s">
+      <c r="CT5" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="CU5" s="107"/>
-      <c r="CV5" s="107"/>
-      <c r="CW5" s="107"/>
-      <c r="CX5" s="107"/>
-      <c r="CY5" s="107"/>
+      <c r="CU5" s="124"/>
+      <c r="CV5" s="124"/>
+      <c r="CW5" s="124"/>
+      <c r="CX5" s="124"/>
+      <c r="CY5" s="124"/>
       <c r="CZ5" s="49"/>
       <c r="DA5" s="49"/>
       <c r="DB5" s="49"/>
@@ -17882,14 +17878,14 @@
       <c r="DF5" s="49"/>
       <c r="DG5" s="49"/>
       <c r="DH5" s="49"/>
-      <c r="DJ5" s="110" t="s">
+      <c r="DJ5" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="DK5" s="107"/>
-      <c r="DL5" s="107"/>
-      <c r="DM5" s="107"/>
-      <c r="DN5" s="107"/>
-      <c r="DO5" s="107"/>
+      <c r="DK5" s="124"/>
+      <c r="DL5" s="124"/>
+      <c r="DM5" s="124"/>
+      <c r="DN5" s="124"/>
+      <c r="DO5" s="124"/>
       <c r="DP5" s="49"/>
       <c r="DQ5" s="49"/>
       <c r="DR5" s="49"/>
@@ -17899,14 +17895,14 @@
       <c r="DV5" s="49"/>
       <c r="DW5" s="49"/>
       <c r="DX5" s="49"/>
-      <c r="DZ5" s="110" t="s">
+      <c r="DZ5" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="EA5" s="107"/>
-      <c r="EB5" s="107"/>
-      <c r="EC5" s="107"/>
-      <c r="ED5" s="107"/>
-      <c r="EE5" s="107"/>
+      <c r="EA5" s="124"/>
+      <c r="EB5" s="124"/>
+      <c r="EC5" s="124"/>
+      <c r="ED5" s="124"/>
+      <c r="EE5" s="124"/>
       <c r="EF5" s="49"/>
       <c r="EG5" s="49"/>
       <c r="EH5" s="49"/>
@@ -17916,14 +17912,14 @@
       <c r="EL5" s="49"/>
       <c r="EM5" s="49"/>
       <c r="EN5" s="49"/>
-      <c r="EP5" s="110" t="s">
+      <c r="EP5" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="EQ5" s="107"/>
-      <c r="ER5" s="107"/>
-      <c r="ES5" s="107"/>
-      <c r="ET5" s="107"/>
-      <c r="EU5" s="107"/>
+      <c r="EQ5" s="124"/>
+      <c r="ER5" s="124"/>
+      <c r="ES5" s="124"/>
+      <c r="ET5" s="124"/>
+      <c r="EU5" s="124"/>
       <c r="EV5" s="49"/>
       <c r="EW5" s="49"/>
       <c r="EX5" s="49"/>
@@ -17938,13 +17934,13 @@
       <c r="B6" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="109" t="s">
+      <c r="C6" s="126" t="s">
         <v>172</v>
       </c>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="107"/>
-      <c r="G6" s="107"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="124"/>
       <c r="H6" s="49"/>
       <c r="I6" s="49"/>
       <c r="J6" s="49"/>
@@ -17957,13 +17953,13 @@
       <c r="R6" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="S6" s="114" t="s">
+      <c r="S6" s="131" t="s">
         <v>226</v>
       </c>
-      <c r="T6" s="112"/>
-      <c r="U6" s="112"/>
-      <c r="V6" s="112"/>
-      <c r="W6" s="112"/>
+      <c r="T6" s="129"/>
+      <c r="U6" s="129"/>
+      <c r="V6" s="129"/>
+      <c r="W6" s="129"/>
       <c r="X6" s="34"/>
       <c r="Y6" s="34"/>
       <c r="Z6" s="34"/>
@@ -17976,13 +17972,13 @@
       <c r="AH6" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="AI6" s="109" t="s">
+      <c r="AI6" s="126" t="s">
         <v>148</v>
       </c>
-      <c r="AJ6" s="107"/>
-      <c r="AK6" s="107"/>
-      <c r="AL6" s="107"/>
-      <c r="AM6" s="107"/>
+      <c r="AJ6" s="124"/>
+      <c r="AK6" s="124"/>
+      <c r="AL6" s="124"/>
+      <c r="AM6" s="124"/>
       <c r="AN6" s="49"/>
       <c r="AO6" s="49"/>
       <c r="AP6" s="49"/>
@@ -17995,13 +17991,13 @@
       <c r="AX6" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="AY6" s="109" t="s">
+      <c r="AY6" s="126" t="s">
         <v>173</v>
       </c>
-      <c r="AZ6" s="107"/>
-      <c r="BA6" s="107"/>
-      <c r="BB6" s="107"/>
-      <c r="BC6" s="107"/>
+      <c r="AZ6" s="124"/>
+      <c r="BA6" s="124"/>
+      <c r="BB6" s="124"/>
+      <c r="BC6" s="124"/>
       <c r="BD6" s="49"/>
       <c r="BE6" s="49"/>
       <c r="BF6" s="49"/>
@@ -18014,13 +18010,13 @@
       <c r="BN6" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="BO6" s="109" t="s">
+      <c r="BO6" s="126" t="s">
         <v>245</v>
       </c>
-      <c r="BP6" s="107"/>
-      <c r="BQ6" s="107"/>
-      <c r="BR6" s="107"/>
-      <c r="BS6" s="107"/>
+      <c r="BP6" s="124"/>
+      <c r="BQ6" s="124"/>
+      <c r="BR6" s="124"/>
+      <c r="BS6" s="124"/>
       <c r="BT6" s="49"/>
       <c r="BU6" s="49"/>
       <c r="BV6" s="49"/>
@@ -18033,13 +18029,13 @@
       <c r="CD6" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="CE6" s="109" t="s">
+      <c r="CE6" s="126" t="s">
         <v>242</v>
       </c>
-      <c r="CF6" s="107"/>
-      <c r="CG6" s="107"/>
-      <c r="CH6" s="107"/>
-      <c r="CI6" s="107"/>
+      <c r="CF6" s="124"/>
+      <c r="CG6" s="124"/>
+      <c r="CH6" s="124"/>
+      <c r="CI6" s="124"/>
       <c r="CJ6" s="49"/>
       <c r="CK6" s="49"/>
       <c r="CL6" s="49"/>
@@ -18052,13 +18048,13 @@
       <c r="CT6" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="CU6" s="109" t="s">
+      <c r="CU6" s="126" t="s">
         <v>258</v>
       </c>
-      <c r="CV6" s="107"/>
-      <c r="CW6" s="107"/>
-      <c r="CX6" s="107"/>
-      <c r="CY6" s="107"/>
+      <c r="CV6" s="124"/>
+      <c r="CW6" s="124"/>
+      <c r="CX6" s="124"/>
+      <c r="CY6" s="124"/>
       <c r="CZ6" s="49"/>
       <c r="DA6" s="49"/>
       <c r="DB6" s="49"/>
@@ -18071,13 +18067,13 @@
       <c r="DJ6" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="DK6" s="109" t="s">
+      <c r="DK6" s="126" t="s">
         <v>232</v>
       </c>
-      <c r="DL6" s="107"/>
-      <c r="DM6" s="107"/>
-      <c r="DN6" s="107"/>
-      <c r="DO6" s="107"/>
+      <c r="DL6" s="124"/>
+      <c r="DM6" s="124"/>
+      <c r="DN6" s="124"/>
+      <c r="DO6" s="124"/>
       <c r="DP6" s="49"/>
       <c r="DQ6" s="49"/>
       <c r="DR6" s="49"/>
@@ -18090,13 +18086,13 @@
       <c r="DZ6" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="EA6" s="109" t="s">
+      <c r="EA6" s="126" t="s">
         <v>249</v>
       </c>
-      <c r="EB6" s="107"/>
-      <c r="EC6" s="107"/>
-      <c r="ED6" s="107"/>
-      <c r="EE6" s="107"/>
+      <c r="EB6" s="124"/>
+      <c r="EC6" s="124"/>
+      <c r="ED6" s="124"/>
+      <c r="EE6" s="124"/>
       <c r="EF6" s="49"/>
       <c r="EG6" s="49"/>
       <c r="EH6" s="49"/>
@@ -18109,13 +18105,13 @@
       <c r="EP6" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="EQ6" s="109" t="s">
+      <c r="EQ6" s="126" t="s">
         <v>237</v>
       </c>
-      <c r="ER6" s="107"/>
-      <c r="ES6" s="107"/>
-      <c r="ET6" s="107"/>
-      <c r="EU6" s="107"/>
+      <c r="ER6" s="124"/>
+      <c r="ES6" s="124"/>
+      <c r="ET6" s="124"/>
+      <c r="EU6" s="124"/>
       <c r="EV6" s="49"/>
       <c r="EW6" s="49"/>
       <c r="EX6" s="49"/>
@@ -18130,13 +18126,13 @@
       <c r="B7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="109" t="s">
+      <c r="C7" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
-      <c r="F7" s="107"/>
-      <c r="G7" s="107"/>
+      <c r="D7" s="124"/>
+      <c r="E7" s="124"/>
+      <c r="F7" s="124"/>
+      <c r="G7" s="124"/>
       <c r="H7" s="49"/>
       <c r="I7" s="49"/>
       <c r="J7" s="49"/>
@@ -18149,13 +18145,13 @@
       <c r="R7" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="S7" s="114" t="s">
+      <c r="S7" s="131" t="s">
         <v>34</v>
       </c>
-      <c r="T7" s="112"/>
-      <c r="U7" s="112"/>
-      <c r="V7" s="112"/>
-      <c r="W7" s="112"/>
+      <c r="T7" s="129"/>
+      <c r="U7" s="129"/>
+      <c r="V7" s="129"/>
+      <c r="W7" s="129"/>
       <c r="X7" s="34"/>
       <c r="Y7" s="34"/>
       <c r="Z7" s="34"/>
@@ -18168,13 +18164,13 @@
       <c r="AH7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="AI7" s="109" t="s">
+      <c r="AI7" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="AJ7" s="107"/>
-      <c r="AK7" s="107"/>
-      <c r="AL7" s="107"/>
-      <c r="AM7" s="107"/>
+      <c r="AJ7" s="124"/>
+      <c r="AK7" s="124"/>
+      <c r="AL7" s="124"/>
+      <c r="AM7" s="124"/>
       <c r="AN7" s="49"/>
       <c r="AO7" s="49"/>
       <c r="AP7" s="49"/>
@@ -18187,13 +18183,13 @@
       <c r="AX7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="AY7" s="109" t="s">
+      <c r="AY7" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="AZ7" s="107"/>
-      <c r="BA7" s="107"/>
-      <c r="BB7" s="107"/>
-      <c r="BC7" s="107"/>
+      <c r="AZ7" s="124"/>
+      <c r="BA7" s="124"/>
+      <c r="BB7" s="124"/>
+      <c r="BC7" s="124"/>
       <c r="BD7" s="49"/>
       <c r="BE7" s="49"/>
       <c r="BF7" s="49"/>
@@ -18206,13 +18202,13 @@
       <c r="BN7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="BO7" s="109" t="s">
+      <c r="BO7" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="BP7" s="107"/>
-      <c r="BQ7" s="107"/>
-      <c r="BR7" s="107"/>
-      <c r="BS7" s="107"/>
+      <c r="BP7" s="124"/>
+      <c r="BQ7" s="124"/>
+      <c r="BR7" s="124"/>
+      <c r="BS7" s="124"/>
       <c r="BT7" s="49"/>
       <c r="BU7" s="49"/>
       <c r="BV7" s="49"/>
@@ -18225,13 +18221,13 @@
       <c r="CD7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="CE7" s="109" t="s">
+      <c r="CE7" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="CF7" s="107"/>
-      <c r="CG7" s="107"/>
-      <c r="CH7" s="107"/>
-      <c r="CI7" s="107"/>
+      <c r="CF7" s="124"/>
+      <c r="CG7" s="124"/>
+      <c r="CH7" s="124"/>
+      <c r="CI7" s="124"/>
       <c r="CJ7" s="49"/>
       <c r="CK7" s="49"/>
       <c r="CL7" s="49"/>
@@ -18244,13 +18240,13 @@
       <c r="CT7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="CU7" s="109" t="s">
+      <c r="CU7" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="CV7" s="107"/>
-      <c r="CW7" s="107"/>
-      <c r="CX7" s="107"/>
-      <c r="CY7" s="107"/>
+      <c r="CV7" s="124"/>
+      <c r="CW7" s="124"/>
+      <c r="CX7" s="124"/>
+      <c r="CY7" s="124"/>
       <c r="CZ7" s="49"/>
       <c r="DA7" s="49"/>
       <c r="DB7" s="49"/>
@@ -18263,13 +18259,13 @@
       <c r="DJ7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="DK7" s="109" t="s">
+      <c r="DK7" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="DL7" s="107"/>
-      <c r="DM7" s="107"/>
-      <c r="DN7" s="107"/>
-      <c r="DO7" s="107"/>
+      <c r="DL7" s="124"/>
+      <c r="DM7" s="124"/>
+      <c r="DN7" s="124"/>
+      <c r="DO7" s="124"/>
       <c r="DP7" s="49"/>
       <c r="DQ7" s="49"/>
       <c r="DR7" s="49"/>
@@ -18282,13 +18278,13 @@
       <c r="DZ7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="EA7" s="109" t="s">
+      <c r="EA7" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="EB7" s="107"/>
-      <c r="EC7" s="107"/>
-      <c r="ED7" s="107"/>
-      <c r="EE7" s="107"/>
+      <c r="EB7" s="124"/>
+      <c r="EC7" s="124"/>
+      <c r="ED7" s="124"/>
+      <c r="EE7" s="124"/>
       <c r="EF7" s="49"/>
       <c r="EG7" s="49"/>
       <c r="EH7" s="49"/>
@@ -18301,13 +18297,13 @@
       <c r="EP7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="EQ7" s="109" t="s">
+      <c r="EQ7" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="ER7" s="107"/>
-      <c r="ES7" s="107"/>
-      <c r="ET7" s="107"/>
-      <c r="EU7" s="107"/>
+      <c r="ER7" s="124"/>
+      <c r="ES7" s="124"/>
+      <c r="ET7" s="124"/>
+      <c r="EU7" s="124"/>
       <c r="EV7" s="49"/>
       <c r="EW7" s="49"/>
       <c r="EX7" s="49"/>
@@ -18322,18 +18318,18 @@
       <c r="B8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="109" t="s">
+      <c r="C8" s="126" t="s">
         <v>144</v>
       </c>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="107"/>
-      <c r="G8" s="107"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="124"/>
       <c r="H8" s="49"/>
-      <c r="I8" s="116" t="s">
+      <c r="I8" s="98" t="s">
         <v>409</v>
       </c>
-      <c r="J8" s="117">
+      <c r="J8" s="99">
         <f>(N43/N13)^(1/30)-1</f>
         <v>2.3977134838169212E-2</v>
       </c>
@@ -18346,18 +18342,18 @@
       <c r="R8" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="S8" s="120" t="s">
+      <c r="S8" s="131" t="s">
         <v>227</v>
       </c>
-      <c r="T8" s="121"/>
-      <c r="U8" s="121"/>
-      <c r="V8" s="121"/>
-      <c r="W8" s="121"/>
+      <c r="T8" s="129"/>
+      <c r="U8" s="129"/>
+      <c r="V8" s="129"/>
+      <c r="W8" s="129"/>
       <c r="X8" s="55"/>
-      <c r="Y8" s="116" t="s">
+      <c r="Y8" s="98" t="s">
         <v>409</v>
       </c>
-      <c r="Z8" s="117">
+      <c r="Z8" s="99">
         <f>(X43/X13)^(1/30)-1</f>
         <v>2.0736944174645666E-2</v>
       </c>
@@ -18370,18 +18366,18 @@
       <c r="AH8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="AI8" s="109" t="s">
+      <c r="AI8" s="126" t="s">
         <v>149</v>
       </c>
-      <c r="AJ8" s="107"/>
-      <c r="AK8" s="107"/>
-      <c r="AL8" s="107"/>
-      <c r="AM8" s="107"/>
+      <c r="AJ8" s="124"/>
+      <c r="AK8" s="124"/>
+      <c r="AL8" s="124"/>
+      <c r="AM8" s="124"/>
       <c r="AN8" s="49"/>
-      <c r="AO8" s="116" t="s">
+      <c r="AO8" s="98" t="s">
         <v>409</v>
       </c>
-      <c r="AP8" s="117">
+      <c r="AP8" s="99">
         <f>(AT43/AT13)^(1/30)-1</f>
         <v>3.5117348400309334E-2</v>
       </c>
@@ -18394,18 +18390,18 @@
       <c r="AX8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="AY8" s="109" t="s">
+      <c r="AY8" s="126" t="s">
         <v>174</v>
       </c>
-      <c r="AZ8" s="107"/>
-      <c r="BA8" s="107"/>
-      <c r="BB8" s="107"/>
-      <c r="BC8" s="107"/>
+      <c r="AZ8" s="124"/>
+      <c r="BA8" s="124"/>
+      <c r="BB8" s="124"/>
+      <c r="BC8" s="124"/>
       <c r="BD8" s="49"/>
-      <c r="BE8" s="116" t="s">
+      <c r="BE8" s="98" t="s">
         <v>409</v>
       </c>
-      <c r="BF8" s="117">
+      <c r="BF8" s="99">
         <f>(BJ43/BJ13)^(1/30)-1</f>
         <v>2.9548225004298212E-2</v>
       </c>
@@ -18418,18 +18414,18 @@
       <c r="BN8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="BO8" s="109" t="s">
+      <c r="BO8" s="126" t="s">
         <v>246</v>
       </c>
-      <c r="BP8" s="107"/>
-      <c r="BQ8" s="107"/>
-      <c r="BR8" s="107"/>
-      <c r="BS8" s="107"/>
+      <c r="BP8" s="124"/>
+      <c r="BQ8" s="124"/>
+      <c r="BR8" s="124"/>
+      <c r="BS8" s="124"/>
       <c r="BT8" s="49"/>
-      <c r="BU8" s="116" t="s">
+      <c r="BU8" s="98" t="s">
         <v>409</v>
       </c>
-      <c r="BV8" s="117">
+      <c r="BV8" s="99">
         <f>(BZ29/BZ13)^(1/16)-1</f>
         <v>6.3201478284775625E-3</v>
       </c>
@@ -18444,18 +18440,18 @@
       <c r="CD8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="CE8" s="109" t="s">
+      <c r="CE8" s="126" t="s">
         <v>243</v>
       </c>
-      <c r="CF8" s="107"/>
-      <c r="CG8" s="107"/>
-      <c r="CH8" s="107"/>
-      <c r="CI8" s="107"/>
+      <c r="CF8" s="124"/>
+      <c r="CG8" s="124"/>
+      <c r="CH8" s="124"/>
+      <c r="CI8" s="124"/>
       <c r="CJ8" s="49"/>
-      <c r="CK8" s="116" t="s">
+      <c r="CK8" s="98" t="s">
         <v>409</v>
       </c>
-      <c r="CL8" s="117">
+      <c r="CL8" s="99">
         <f>(CP43/CP13)^(1/30)-1</f>
         <v>2.5219757035239265E-2</v>
       </c>
@@ -18468,18 +18464,18 @@
       <c r="CT8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="CU8" s="109" t="s">
+      <c r="CU8" s="126" t="s">
         <v>259</v>
       </c>
-      <c r="CV8" s="107"/>
-      <c r="CW8" s="107"/>
-      <c r="CX8" s="107"/>
-      <c r="CY8" s="107"/>
+      <c r="CV8" s="124"/>
+      <c r="CW8" s="124"/>
+      <c r="CX8" s="124"/>
+      <c r="CY8" s="124"/>
       <c r="CZ8" s="49"/>
-      <c r="DA8" s="116" t="s">
+      <c r="DA8" s="98" t="s">
         <v>409</v>
       </c>
-      <c r="DB8" s="117">
+      <c r="DB8" s="99">
         <f>(DF42/DF13)^(1/29)-1</f>
         <v>5.2913605158896315E-2</v>
       </c>
@@ -18493,18 +18489,18 @@
       <c r="DJ8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="DK8" s="109" t="s">
+      <c r="DK8" s="126" t="s">
         <v>233</v>
       </c>
-      <c r="DL8" s="107"/>
-      <c r="DM8" s="107"/>
-      <c r="DN8" s="107"/>
-      <c r="DO8" s="107"/>
+      <c r="DL8" s="124"/>
+      <c r="DM8" s="124"/>
+      <c r="DN8" s="124"/>
+      <c r="DO8" s="124"/>
       <c r="DP8" s="49"/>
-      <c r="DQ8" s="116" t="s">
+      <c r="DQ8" s="98" t="s">
         <v>409</v>
       </c>
-      <c r="DR8" s="117">
+      <c r="DR8" s="99">
         <f>(DS42/DS14)^(1/28)-1</f>
         <v>5.2018836646548605E-2</v>
       </c>
@@ -18517,18 +18513,18 @@
       <c r="DZ8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="EA8" s="109" t="s">
+      <c r="EA8" s="126" t="s">
         <v>139</v>
       </c>
-      <c r="EB8" s="107"/>
-      <c r="EC8" s="107"/>
-      <c r="ED8" s="107"/>
-      <c r="EE8" s="107"/>
+      <c r="EB8" s="124"/>
+      <c r="EC8" s="124"/>
+      <c r="ED8" s="124"/>
+      <c r="EE8" s="124"/>
       <c r="EF8" s="49"/>
-      <c r="EG8" s="116" t="s">
+      <c r="EG8" s="98" t="s">
         <v>409</v>
       </c>
-      <c r="EH8" s="117">
+      <c r="EH8" s="99">
         <f>(EL43/EL13)^(1/30)-1</f>
         <v>5.2900906226266198E-2</v>
       </c>
@@ -18541,18 +18537,18 @@
       <c r="EP8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="EQ8" s="109" t="s">
+      <c r="EQ8" s="126" t="s">
         <v>238</v>
       </c>
-      <c r="ER8" s="107"/>
-      <c r="ES8" s="107"/>
-      <c r="ET8" s="107"/>
-      <c r="EU8" s="107"/>
+      <c r="ER8" s="124"/>
+      <c r="ES8" s="124"/>
+      <c r="ET8" s="124"/>
+      <c r="EU8" s="124"/>
       <c r="EV8" s="49"/>
-      <c r="EW8" s="116" t="s">
+      <c r="EW8" s="98" t="s">
         <v>409</v>
       </c>
-      <c r="EX8" s="117">
+      <c r="EX8" s="99">
         <f>(FB29/FB14)^(1/15)-1</f>
         <v>7.3233117948781068E-3</v>
       </c>
@@ -18567,18 +18563,18 @@
       <c r="B9" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="109" t="s">
+      <c r="C9" s="126" t="s">
         <v>150</v>
       </c>
-      <c r="D9" s="107"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="107"/>
-      <c r="G9" s="107"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="124"/>
       <c r="H9" s="49"/>
-      <c r="I9" s="116" t="s">
+      <c r="I9" s="98" t="s">
         <v>410</v>
       </c>
-      <c r="J9" s="118"/>
+      <c r="J9" s="100"/>
       <c r="K9" s="49"/>
       <c r="L9" s="49"/>
       <c r="M9" s="49"/>
@@ -18588,18 +18584,18 @@
       <c r="R9" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="114" t="s">
+      <c r="S9" s="131" t="s">
         <v>228</v>
       </c>
-      <c r="T9" s="112"/>
-      <c r="U9" s="112"/>
-      <c r="V9" s="112"/>
-      <c r="W9" s="112"/>
+      <c r="T9" s="129"/>
+      <c r="U9" s="129"/>
+      <c r="V9" s="129"/>
+      <c r="W9" s="129"/>
       <c r="X9" s="34"/>
-      <c r="Y9" s="116" t="s">
+      <c r="Y9" s="98" t="s">
         <v>410</v>
       </c>
-      <c r="Z9" s="119"/>
+      <c r="Z9" s="101"/>
       <c r="AA9" s="34"/>
       <c r="AB9" s="34"/>
       <c r="AC9" s="34"/>
@@ -18609,18 +18605,18 @@
       <c r="AH9" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="AI9" s="109" t="s">
+      <c r="AI9" s="126" t="s">
         <v>150</v>
       </c>
-      <c r="AJ9" s="107"/>
-      <c r="AK9" s="107"/>
-      <c r="AL9" s="107"/>
-      <c r="AM9" s="107"/>
+      <c r="AJ9" s="124"/>
+      <c r="AK9" s="124"/>
+      <c r="AL9" s="124"/>
+      <c r="AM9" s="124"/>
       <c r="AN9" s="49"/>
-      <c r="AO9" s="116" t="s">
+      <c r="AO9" s="98" t="s">
         <v>410</v>
       </c>
-      <c r="AP9" s="118"/>
+      <c r="AP9" s="100"/>
       <c r="AQ9" s="49"/>
       <c r="AR9" s="49"/>
       <c r="AS9" s="49"/>
@@ -18630,18 +18626,18 @@
       <c r="AX9" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="AY9" s="109" t="s">
+      <c r="AY9" s="126" t="s">
         <v>150</v>
       </c>
-      <c r="AZ9" s="107"/>
-      <c r="BA9" s="107"/>
-      <c r="BB9" s="107"/>
-      <c r="BC9" s="107"/>
+      <c r="AZ9" s="124"/>
+      <c r="BA9" s="124"/>
+      <c r="BB9" s="124"/>
+      <c r="BC9" s="124"/>
       <c r="BD9" s="49"/>
-      <c r="BE9" s="116" t="s">
+      <c r="BE9" s="98" t="s">
         <v>410</v>
       </c>
-      <c r="BF9" s="118"/>
+      <c r="BF9" s="100"/>
       <c r="BG9" s="49"/>
       <c r="BH9" s="49"/>
       <c r="BI9" s="49"/>
@@ -18651,18 +18647,18 @@
       <c r="BN9" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="BO9" s="109" t="s">
+      <c r="BO9" s="126" t="s">
         <v>239</v>
       </c>
-      <c r="BP9" s="107"/>
-      <c r="BQ9" s="107"/>
-      <c r="BR9" s="107"/>
-      <c r="BS9" s="107"/>
+      <c r="BP9" s="124"/>
+      <c r="BQ9" s="124"/>
+      <c r="BR9" s="124"/>
+      <c r="BS9" s="124"/>
       <c r="BT9" s="49"/>
-      <c r="BU9" s="116" t="s">
+      <c r="BU9" s="98" t="s">
         <v>410</v>
       </c>
-      <c r="BV9" s="118"/>
+      <c r="BV9" s="100"/>
       <c r="BW9" s="49"/>
       <c r="BX9" s="49"/>
       <c r="BY9" s="49"/>
@@ -18672,18 +18668,18 @@
       <c r="CD9" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="CE9" s="109" t="s">
+      <c r="CE9" s="126" t="s">
         <v>150</v>
       </c>
-      <c r="CF9" s="107"/>
-      <c r="CG9" s="107"/>
-      <c r="CH9" s="107"/>
-      <c r="CI9" s="107"/>
+      <c r="CF9" s="124"/>
+      <c r="CG9" s="124"/>
+      <c r="CH9" s="124"/>
+      <c r="CI9" s="124"/>
       <c r="CJ9" s="49"/>
-      <c r="CK9" s="116" t="s">
+      <c r="CK9" s="98" t="s">
         <v>410</v>
       </c>
-      <c r="CL9" s="118"/>
+      <c r="CL9" s="100"/>
       <c r="CM9" s="49"/>
       <c r="CN9" s="49"/>
       <c r="CO9" s="49"/>
@@ -18693,18 +18689,18 @@
       <c r="CT9" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="CU9" s="109" t="s">
+      <c r="CU9" s="126" t="s">
         <v>234</v>
       </c>
-      <c r="CV9" s="107"/>
-      <c r="CW9" s="107"/>
-      <c r="CX9" s="107"/>
-      <c r="CY9" s="107"/>
+      <c r="CV9" s="124"/>
+      <c r="CW9" s="124"/>
+      <c r="CX9" s="124"/>
+      <c r="CY9" s="124"/>
       <c r="CZ9" s="49"/>
-      <c r="DA9" s="116" t="s">
+      <c r="DA9" s="98" t="s">
         <v>410</v>
       </c>
-      <c r="DB9" s="118"/>
+      <c r="DB9" s="100"/>
       <c r="DC9" s="49"/>
       <c r="DD9" s="49"/>
       <c r="DE9" s="49"/>
@@ -18714,18 +18710,18 @@
       <c r="DJ9" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="DK9" s="109" t="s">
+      <c r="DK9" s="126" t="s">
         <v>234</v>
       </c>
-      <c r="DL9" s="107"/>
-      <c r="DM9" s="107"/>
-      <c r="DN9" s="107"/>
-      <c r="DO9" s="107"/>
+      <c r="DL9" s="124"/>
+      <c r="DM9" s="124"/>
+      <c r="DN9" s="124"/>
+      <c r="DO9" s="124"/>
       <c r="DP9" s="49"/>
-      <c r="DQ9" s="116" t="s">
+      <c r="DQ9" s="98" t="s">
         <v>410</v>
       </c>
-      <c r="DR9" s="118"/>
+      <c r="DR9" s="100"/>
       <c r="DS9" s="49"/>
       <c r="DT9" s="49"/>
       <c r="DU9" s="49"/>
@@ -18735,18 +18731,18 @@
       <c r="DZ9" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="EA9" s="109" t="s">
+      <c r="EA9" s="126" t="s">
         <v>228</v>
       </c>
-      <c r="EB9" s="107"/>
-      <c r="EC9" s="107"/>
-      <c r="ED9" s="107"/>
-      <c r="EE9" s="107"/>
+      <c r="EB9" s="124"/>
+      <c r="EC9" s="124"/>
+      <c r="ED9" s="124"/>
+      <c r="EE9" s="124"/>
       <c r="EF9" s="49"/>
-      <c r="EG9" s="116" t="s">
+      <c r="EG9" s="98" t="s">
         <v>410</v>
       </c>
-      <c r="EH9" s="118"/>
+      <c r="EH9" s="100"/>
       <c r="EI9" s="49"/>
       <c r="EJ9" s="49"/>
       <c r="EK9" s="49"/>
@@ -18756,18 +18752,18 @@
       <c r="EP9" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="EQ9" s="109" t="s">
+      <c r="EQ9" s="126" t="s">
         <v>239</v>
       </c>
-      <c r="ER9" s="107"/>
-      <c r="ES9" s="107"/>
-      <c r="ET9" s="107"/>
-      <c r="EU9" s="107"/>
+      <c r="ER9" s="124"/>
+      <c r="ES9" s="124"/>
+      <c r="ET9" s="124"/>
+      <c r="EU9" s="124"/>
       <c r="EV9" s="49"/>
-      <c r="EW9" s="116" t="s">
+      <c r="EW9" s="98" t="s">
         <v>410</v>
       </c>
-      <c r="EX9" s="118"/>
+      <c r="EX9" s="100"/>
       <c r="EY9" s="49"/>
       <c r="EZ9" s="49"/>
       <c r="FA9" s="49"/>
@@ -18779,13 +18775,13 @@
       <c r="B10" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="C10" s="106" t="s">
+      <c r="C10" s="123" t="s">
         <v>230</v>
       </c>
-      <c r="D10" s="107"/>
-      <c r="E10" s="107"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="107"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="124"/>
       <c r="H10" s="49"/>
       <c r="I10" s="49"/>
       <c r="J10" s="49"/>
@@ -18798,13 +18794,13 @@
       <c r="R10" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="S10" s="113" t="s">
+      <c r="S10" s="130" t="s">
         <v>230</v>
       </c>
-      <c r="T10" s="112"/>
-      <c r="U10" s="112"/>
-      <c r="V10" s="112"/>
-      <c r="W10" s="112"/>
+      <c r="T10" s="129"/>
+      <c r="U10" s="129"/>
+      <c r="V10" s="129"/>
+      <c r="W10" s="129"/>
       <c r="X10" s="34"/>
       <c r="Y10" s="34"/>
       <c r="Z10" s="34"/>
@@ -18817,13 +18813,13 @@
       <c r="AH10" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="AI10" s="106" t="s">
+      <c r="AI10" s="123" t="s">
         <v>230</v>
       </c>
-      <c r="AJ10" s="107"/>
-      <c r="AK10" s="107"/>
-      <c r="AL10" s="107"/>
-      <c r="AM10" s="107"/>
+      <c r="AJ10" s="124"/>
+      <c r="AK10" s="124"/>
+      <c r="AL10" s="124"/>
+      <c r="AM10" s="124"/>
       <c r="AN10" s="49"/>
       <c r="AO10" s="49"/>
       <c r="AP10" s="49"/>
@@ -18836,13 +18832,13 @@
       <c r="AX10" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="AY10" s="106" t="s">
+      <c r="AY10" s="123" t="s">
         <v>230</v>
       </c>
-      <c r="AZ10" s="107"/>
-      <c r="BA10" s="107"/>
-      <c r="BB10" s="107"/>
-      <c r="BC10" s="107"/>
+      <c r="AZ10" s="124"/>
+      <c r="BA10" s="124"/>
+      <c r="BB10" s="124"/>
+      <c r="BC10" s="124"/>
       <c r="BD10" s="49"/>
       <c r="BE10" s="49"/>
       <c r="BF10" s="49"/>
@@ -18855,13 +18851,13 @@
       <c r="BN10" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="BO10" s="106" t="s">
+      <c r="BO10" s="123" t="s">
         <v>240</v>
       </c>
-      <c r="BP10" s="107"/>
-      <c r="BQ10" s="107"/>
-      <c r="BR10" s="107"/>
-      <c r="BS10" s="107"/>
+      <c r="BP10" s="124"/>
+      <c r="BQ10" s="124"/>
+      <c r="BR10" s="124"/>
+      <c r="BS10" s="124"/>
       <c r="BT10" s="49"/>
       <c r="BU10" s="49"/>
       <c r="BV10" s="49"/>
@@ -18874,13 +18870,13 @@
       <c r="CD10" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="CE10" s="106" t="s">
+      <c r="CE10" s="123" t="s">
         <v>230</v>
       </c>
-      <c r="CF10" s="107"/>
-      <c r="CG10" s="107"/>
-      <c r="CH10" s="107"/>
-      <c r="CI10" s="107"/>
+      <c r="CF10" s="124"/>
+      <c r="CG10" s="124"/>
+      <c r="CH10" s="124"/>
+      <c r="CI10" s="124"/>
       <c r="CJ10" s="49"/>
       <c r="CK10" s="49"/>
       <c r="CL10" s="49"/>
@@ -18893,13 +18889,13 @@
       <c r="CT10" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="CU10" s="106" t="s">
+      <c r="CU10" s="123" t="s">
         <v>235</v>
       </c>
-      <c r="CV10" s="107"/>
-      <c r="CW10" s="107"/>
-      <c r="CX10" s="107"/>
-      <c r="CY10" s="107"/>
+      <c r="CV10" s="124"/>
+      <c r="CW10" s="124"/>
+      <c r="CX10" s="124"/>
+      <c r="CY10" s="124"/>
       <c r="CZ10" s="49"/>
       <c r="DA10" s="49"/>
       <c r="DB10" s="49"/>
@@ -18912,13 +18908,13 @@
       <c r="DJ10" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="DK10" s="106" t="s">
+      <c r="DK10" s="123" t="s">
         <v>235</v>
       </c>
-      <c r="DL10" s="107"/>
-      <c r="DM10" s="107"/>
-      <c r="DN10" s="107"/>
-      <c r="DO10" s="107"/>
+      <c r="DL10" s="124"/>
+      <c r="DM10" s="124"/>
+      <c r="DN10" s="124"/>
+      <c r="DO10" s="124"/>
       <c r="DP10" s="49"/>
       <c r="DQ10" s="49"/>
       <c r="DR10" s="49"/>
@@ -18931,13 +18927,13 @@
       <c r="DZ10" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="EA10" s="106" t="s">
+      <c r="EA10" s="123" t="s">
         <v>230</v>
       </c>
-      <c r="EB10" s="107"/>
-      <c r="EC10" s="107"/>
-      <c r="ED10" s="107"/>
-      <c r="EE10" s="107"/>
+      <c r="EB10" s="124"/>
+      <c r="EC10" s="124"/>
+      <c r="ED10" s="124"/>
+      <c r="EE10" s="124"/>
       <c r="EF10" s="49"/>
       <c r="EG10" s="49"/>
       <c r="EH10" s="49"/>
@@ -18950,13 +18946,13 @@
       <c r="EP10" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="EQ10" s="106" t="s">
+      <c r="EQ10" s="123" t="s">
         <v>240</v>
       </c>
-      <c r="ER10" s="107"/>
-      <c r="ES10" s="107"/>
-      <c r="ET10" s="107"/>
-      <c r="EU10" s="107"/>
+      <c r="ER10" s="124"/>
+      <c r="ES10" s="124"/>
+      <c r="ET10" s="124"/>
+      <c r="EU10" s="124"/>
       <c r="EV10" s="49"/>
       <c r="EW10" s="49"/>
       <c r="EX10" s="49"/>
@@ -31140,14 +31136,14 @@
       <c r="EN43" s="49"/>
     </row>
     <row r="45" spans="2:144" x14ac:dyDescent="0.25">
-      <c r="R45" s="108" t="s">
+      <c r="R45" s="125" t="s">
         <v>223</v>
       </c>
-      <c r="S45" s="107"/>
-      <c r="T45" s="107"/>
-      <c r="U45" s="107"/>
-      <c r="V45" s="107"/>
-      <c r="W45" s="107"/>
+      <c r="S45" s="124"/>
+      <c r="T45" s="124"/>
+      <c r="U45" s="124"/>
+      <c r="V45" s="124"/>
+      <c r="W45" s="124"/>
       <c r="X45" s="49"/>
       <c r="Y45" s="49"/>
       <c r="Z45" s="49"/>
@@ -31159,14 +31155,14 @@
       <c r="AF45" s="49"/>
     </row>
     <row r="46" spans="2:144" x14ac:dyDescent="0.25">
-      <c r="R46" s="108" t="s">
+      <c r="R46" s="125" t="s">
         <v>224</v>
       </c>
-      <c r="S46" s="107"/>
-      <c r="T46" s="107"/>
-      <c r="U46" s="107"/>
-      <c r="V46" s="107"/>
-      <c r="W46" s="107"/>
+      <c r="S46" s="124"/>
+      <c r="T46" s="124"/>
+      <c r="U46" s="124"/>
+      <c r="V46" s="124"/>
+      <c r="W46" s="124"/>
       <c r="X46" s="49"/>
       <c r="Y46" s="49"/>
       <c r="Z46" s="49"/>
@@ -31178,12 +31174,12 @@
       <c r="AF46" s="49"/>
     </row>
     <row r="47" spans="2:144" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R47" s="107"/>
-      <c r="S47" s="107"/>
-      <c r="T47" s="107"/>
-      <c r="U47" s="107"/>
-      <c r="V47" s="107"/>
-      <c r="W47" s="107"/>
+      <c r="R47" s="124"/>
+      <c r="S47" s="124"/>
+      <c r="T47" s="124"/>
+      <c r="U47" s="124"/>
+      <c r="V47" s="124"/>
+      <c r="W47" s="124"/>
       <c r="X47" s="49"/>
       <c r="Y47" s="49"/>
       <c r="Z47" s="49"/>
@@ -31198,13 +31194,13 @@
       <c r="R48" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="S48" s="109" t="s">
+      <c r="S48" s="126" t="s">
         <v>225</v>
       </c>
-      <c r="T48" s="107"/>
-      <c r="U48" s="107"/>
-      <c r="V48" s="107"/>
-      <c r="W48" s="107"/>
+      <c r="T48" s="124"/>
+      <c r="U48" s="124"/>
+      <c r="V48" s="124"/>
+      <c r="W48" s="124"/>
       <c r="X48" s="49"/>
       <c r="Y48" s="49"/>
       <c r="Z48" s="49"/>
@@ -31216,14 +31212,14 @@
       <c r="AF48" s="49"/>
     </row>
     <row r="49" spans="18:32" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R49" s="110" t="s">
+      <c r="R49" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="S49" s="107"/>
-      <c r="T49" s="107"/>
-      <c r="U49" s="107"/>
-      <c r="V49" s="107"/>
-      <c r="W49" s="107"/>
+      <c r="S49" s="124"/>
+      <c r="T49" s="124"/>
+      <c r="U49" s="124"/>
+      <c r="V49" s="124"/>
+      <c r="W49" s="124"/>
       <c r="X49" s="49"/>
       <c r="Y49" s="49"/>
       <c r="Z49" s="49"/>
@@ -31238,13 +31234,13 @@
       <c r="R50" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="S50" s="109" t="s">
+      <c r="S50" s="126" t="s">
         <v>226</v>
       </c>
-      <c r="T50" s="107"/>
-      <c r="U50" s="107"/>
-      <c r="V50" s="107"/>
-      <c r="W50" s="107"/>
+      <c r="T50" s="124"/>
+      <c r="U50" s="124"/>
+      <c r="V50" s="124"/>
+      <c r="W50" s="124"/>
       <c r="X50" s="49"/>
       <c r="Y50" s="49"/>
       <c r="Z50" s="49"/>
@@ -31259,13 +31255,13 @@
       <c r="R51" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="S51" s="109" t="s">
+      <c r="S51" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="T51" s="107"/>
-      <c r="U51" s="107"/>
-      <c r="V51" s="107"/>
-      <c r="W51" s="107"/>
+      <c r="T51" s="124"/>
+      <c r="U51" s="124"/>
+      <c r="V51" s="124"/>
+      <c r="W51" s="124"/>
       <c r="X51" s="49"/>
       <c r="Y51" s="49"/>
       <c r="Z51" s="49"/>
@@ -31280,13 +31276,13 @@
       <c r="R52" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="S52" s="109" t="s">
+      <c r="S52" s="126" t="s">
         <v>227</v>
       </c>
-      <c r="T52" s="107"/>
-      <c r="U52" s="107"/>
-      <c r="V52" s="107"/>
-      <c r="W52" s="107"/>
+      <c r="T52" s="124"/>
+      <c r="U52" s="124"/>
+      <c r="V52" s="124"/>
+      <c r="W52" s="124"/>
       <c r="X52" s="49"/>
       <c r="Y52" s="49"/>
       <c r="Z52" s="49"/>
@@ -31301,13 +31297,13 @@
       <c r="R53" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="S53" s="109" t="s">
+      <c r="S53" s="126" t="s">
         <v>228</v>
       </c>
-      <c r="T53" s="107"/>
-      <c r="U53" s="107"/>
-      <c r="V53" s="107"/>
-      <c r="W53" s="107"/>
+      <c r="T53" s="124"/>
+      <c r="U53" s="124"/>
+      <c r="V53" s="124"/>
+      <c r="W53" s="124"/>
       <c r="X53" s="49"/>
       <c r="Y53" s="49"/>
       <c r="Z53" s="49"/>
@@ -31322,13 +31318,13 @@
       <c r="R54" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="S54" s="106" t="s">
+      <c r="S54" s="123" t="s">
         <v>230</v>
       </c>
-      <c r="T54" s="107"/>
-      <c r="U54" s="107"/>
-      <c r="V54" s="107"/>
-      <c r="W54" s="107"/>
+      <c r="T54" s="124"/>
+      <c r="U54" s="124"/>
+      <c r="V54" s="124"/>
+      <c r="W54" s="124"/>
       <c r="X54" s="49"/>
       <c r="Y54" s="49"/>
       <c r="Z54" s="49"/>
@@ -32709,38 +32705,60 @@
     </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="EA10:EE10"/>
-    <mergeCell ref="DJ1:DO1"/>
-    <mergeCell ref="DJ2:DO2"/>
-    <mergeCell ref="DJ3:DO3"/>
-    <mergeCell ref="DK4:DO4"/>
-    <mergeCell ref="DK6:DO6"/>
-    <mergeCell ref="DK7:DO7"/>
-    <mergeCell ref="DK8:DO8"/>
-    <mergeCell ref="DK9:DO9"/>
-    <mergeCell ref="DJ5:DO5"/>
-    <mergeCell ref="DK10:DO10"/>
-    <mergeCell ref="DZ1:EE1"/>
-    <mergeCell ref="DZ2:EE2"/>
-    <mergeCell ref="DZ3:EE3"/>
-    <mergeCell ref="EA4:EE4"/>
-    <mergeCell ref="DZ5:EE5"/>
-    <mergeCell ref="EA6:EE6"/>
-    <mergeCell ref="EA7:EE7"/>
-    <mergeCell ref="EA8:EE8"/>
-    <mergeCell ref="EA9:EE9"/>
-    <mergeCell ref="CE9:CI9"/>
-    <mergeCell ref="BO10:BS10"/>
-    <mergeCell ref="CU6:CY6"/>
-    <mergeCell ref="CU7:CY7"/>
-    <mergeCell ref="CU8:CY8"/>
-    <mergeCell ref="CU9:CY9"/>
-    <mergeCell ref="CU10:CY10"/>
-    <mergeCell ref="CT1:CY1"/>
-    <mergeCell ref="CT2:CY2"/>
-    <mergeCell ref="CT3:CY3"/>
-    <mergeCell ref="CU4:CY4"/>
-    <mergeCell ref="CT5:CY5"/>
+    <mergeCell ref="EQ10:EU10"/>
+    <mergeCell ref="EP1:EU1"/>
+    <mergeCell ref="EP2:EU2"/>
+    <mergeCell ref="EP3:EU3"/>
+    <mergeCell ref="EQ4:EU4"/>
+    <mergeCell ref="EP5:EU5"/>
+    <mergeCell ref="EQ6:EU6"/>
+    <mergeCell ref="EQ7:EU7"/>
+    <mergeCell ref="EQ8:EU8"/>
+    <mergeCell ref="EQ9:EU9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="R1:W1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="S10:W10"/>
+    <mergeCell ref="S7:W7"/>
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="S4:W4"/>
+    <mergeCell ref="R5:W5"/>
+    <mergeCell ref="S6:W6"/>
+    <mergeCell ref="R2:W2"/>
+    <mergeCell ref="R3:W3"/>
+    <mergeCell ref="AY10:BC10"/>
+    <mergeCell ref="S53:W53"/>
+    <mergeCell ref="S54:W54"/>
+    <mergeCell ref="AH1:AM1"/>
+    <mergeCell ref="AH2:AM2"/>
+    <mergeCell ref="AH3:AM3"/>
+    <mergeCell ref="AI4:AM4"/>
+    <mergeCell ref="AH5:AM5"/>
+    <mergeCell ref="AI6:AM6"/>
+    <mergeCell ref="AI7:AM7"/>
+    <mergeCell ref="AI8:AM8"/>
+    <mergeCell ref="AI9:AM9"/>
+    <mergeCell ref="AI10:AM10"/>
+    <mergeCell ref="R45:W45"/>
+    <mergeCell ref="R46:W46"/>
+    <mergeCell ref="R47:W47"/>
+    <mergeCell ref="S48:W48"/>
+    <mergeCell ref="R49:W49"/>
+    <mergeCell ref="S50:W50"/>
+    <mergeCell ref="S51:W51"/>
+    <mergeCell ref="S52:W52"/>
+    <mergeCell ref="AX1:BC1"/>
+    <mergeCell ref="AX2:BC2"/>
+    <mergeCell ref="AX3:BC3"/>
     <mergeCell ref="AY4:BC4"/>
     <mergeCell ref="AX5:BC5"/>
     <mergeCell ref="AY6:BC6"/>
@@ -32765,60 +32783,38 @@
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CE7:CI7"/>
     <mergeCell ref="CE8:CI8"/>
-    <mergeCell ref="AY10:BC10"/>
-    <mergeCell ref="S53:W53"/>
-    <mergeCell ref="S54:W54"/>
-    <mergeCell ref="AH1:AM1"/>
-    <mergeCell ref="AH2:AM2"/>
-    <mergeCell ref="AH3:AM3"/>
-    <mergeCell ref="AI4:AM4"/>
-    <mergeCell ref="AH5:AM5"/>
-    <mergeCell ref="AI6:AM6"/>
-    <mergeCell ref="AI7:AM7"/>
-    <mergeCell ref="AI8:AM8"/>
-    <mergeCell ref="AI9:AM9"/>
-    <mergeCell ref="AI10:AM10"/>
-    <mergeCell ref="R45:W45"/>
-    <mergeCell ref="R46:W46"/>
-    <mergeCell ref="R47:W47"/>
-    <mergeCell ref="S48:W48"/>
-    <mergeCell ref="R49:W49"/>
-    <mergeCell ref="S50:W50"/>
-    <mergeCell ref="S51:W51"/>
-    <mergeCell ref="S52:W52"/>
-    <mergeCell ref="AX1:BC1"/>
-    <mergeCell ref="AX2:BC2"/>
-    <mergeCell ref="AX3:BC3"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="R1:W1"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="S10:W10"/>
-    <mergeCell ref="S7:W7"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="S4:W4"/>
-    <mergeCell ref="R5:W5"/>
-    <mergeCell ref="S6:W6"/>
-    <mergeCell ref="R2:W2"/>
-    <mergeCell ref="R3:W3"/>
-    <mergeCell ref="EQ10:EU10"/>
-    <mergeCell ref="EP1:EU1"/>
-    <mergeCell ref="EP2:EU2"/>
-    <mergeCell ref="EP3:EU3"/>
-    <mergeCell ref="EQ4:EU4"/>
-    <mergeCell ref="EP5:EU5"/>
-    <mergeCell ref="EQ6:EU6"/>
-    <mergeCell ref="EQ7:EU7"/>
-    <mergeCell ref="EQ8:EU8"/>
-    <mergeCell ref="EQ9:EU9"/>
+    <mergeCell ref="CE9:CI9"/>
+    <mergeCell ref="BO10:BS10"/>
+    <mergeCell ref="CU6:CY6"/>
+    <mergeCell ref="CU7:CY7"/>
+    <mergeCell ref="CU8:CY8"/>
+    <mergeCell ref="CU9:CY9"/>
+    <mergeCell ref="CU10:CY10"/>
+    <mergeCell ref="CT1:CY1"/>
+    <mergeCell ref="CT2:CY2"/>
+    <mergeCell ref="CT3:CY3"/>
+    <mergeCell ref="CU4:CY4"/>
+    <mergeCell ref="CT5:CY5"/>
+    <mergeCell ref="EA10:EE10"/>
+    <mergeCell ref="DJ1:DO1"/>
+    <mergeCell ref="DJ2:DO2"/>
+    <mergeCell ref="DJ3:DO3"/>
+    <mergeCell ref="DK4:DO4"/>
+    <mergeCell ref="DK6:DO6"/>
+    <mergeCell ref="DK7:DO7"/>
+    <mergeCell ref="DK8:DO8"/>
+    <mergeCell ref="DK9:DO9"/>
+    <mergeCell ref="DJ5:DO5"/>
+    <mergeCell ref="DK10:DO10"/>
+    <mergeCell ref="DZ1:EE1"/>
+    <mergeCell ref="DZ2:EE2"/>
+    <mergeCell ref="DZ3:EE3"/>
+    <mergeCell ref="EA4:EE4"/>
+    <mergeCell ref="DZ5:EE5"/>
+    <mergeCell ref="EA6:EE6"/>
+    <mergeCell ref="EA7:EE7"/>
+    <mergeCell ref="EA8:EE8"/>
+    <mergeCell ref="EA9:EE9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/EconAutomation/src/supporting_docs/econ_wb_templates/WorkingCalc_Current.xlsx
+++ b/EconAutomation/src/supporting_docs/econ_wb_templates/WorkingCalc_Current.xlsx
@@ -9,10 +9,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EricBussey\GitHub\EconAutomation-REP\EconAutomation\src\supporting_docs\econ_wb_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACC5C77-3153-49AF-A98A-0B803BD0EF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBDB335-2BA8-4624-AECE-EF0668F40BD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" tabRatio="808" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{FDA883B1-89AA-41DF-A01F-246993B8D400}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" tabRatio="808" firstSheet="6" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="14" xr2:uid="{FDA883B1-89AA-41DF-A01F-246993B8D400}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORT_OUTPUTS" sheetId="30" r:id="rId1"/>
@@ -29,13 +29,16 @@
     <sheet name="Pivoted_By_Year" sheetId="14" r:id="rId12"/>
     <sheet name="AppOptions" sheetId="16" r:id="rId13"/>
     <sheet name="Options " sheetId="15" r:id="rId14"/>
-    <sheet name="GetBloombergDailyYieldCurve_cur" sheetId="8" r:id="rId15"/>
+    <sheet name="Discount Rates" sheetId="8" r:id="rId15"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId16"/>
+  </externalReferences>
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="12" hidden="1">AppOptions!$A$1:$B$9</definedName>
     <definedName name="ExternalData_1" localSheetId="6" hidden="1">DepletionOfFunds!$A$1:$O$59</definedName>
+    <definedName name="ExternalData_1" localSheetId="14" hidden="1">'Discount Rates'!$A$2:$C$32</definedName>
     <definedName name="ExternalData_1" localSheetId="7" hidden="1">Future_Cost_By_Year!$A$1:$D$17</definedName>
-    <definedName name="ExternalData_1" localSheetId="14" hidden="1">GetBloombergDailyYieldCurve_cur!$A$1:$C$31</definedName>
     <definedName name="ExternalData_1" localSheetId="5" hidden="1">'Roll Up'!$A$1:$AU$49</definedName>
     <definedName name="ExternalData_2" localSheetId="11" hidden="1">Pivoted_By_Year!$A$1:$J$2</definedName>
     <definedName name="ExternalData_2" localSheetId="10" hidden="1">PV_Totals_By_Item!$A$1:$G$6</definedName>
@@ -143,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="439">
   <si>
     <t>Item Name</t>
   </si>
@@ -1389,12 +1392,6 @@
     <t>Rate High</t>
   </si>
   <si>
-    <t>PASTED YEAR</t>
-  </si>
-  <si>
-    <t>PASTED DISCOUNT RATES</t>
-  </si>
-  <si>
     <t>J8</t>
   </si>
   <si>
@@ -1453,13 +1450,37 @@
   </si>
   <si>
     <t>EX9</t>
+  </si>
+  <si>
+    <t>start offset</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>e.g., 10</t>
+  </si>
+  <si>
+    <t>e.g., 5</t>
+  </si>
+  <si>
+    <t>IN WORKING_CALC, FIRST FULL CALENDAR YEAR IS FIRST YEAR</t>
+  </si>
+  <si>
+    <t>REQUIRES:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Years 10 - 15 </t>
+  </si>
+  <si>
+    <t>BLOOMBERG DISCOUNT RATES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
@@ -1467,8 +1488,9 @@
     <numFmt numFmtId="166" formatCode="#0.0"/>
     <numFmt numFmtId="167" formatCode="#0.000"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="mm/dd/yyyy\ hh:mm\ AM/PM"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1607,8 +1629,44 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1717,8 +1775,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor theme="8" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor theme="8" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="41">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -2214,6 +2290,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2221,7 +2346,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2529,6 +2654,43 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="21" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="20" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="21" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -2536,7 +2698,7 @@
     <cellStyle name="Normal 2" xfId="3" xr:uid="{831D47E7-1FBF-4008-8E47-36EB08CBC9FC}"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="116">
+  <dxfs count="112">
     <dxf>
       <fill>
         <patternFill>
@@ -2606,119 +2768,6 @@
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14999847407452621"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14999847407452621"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14999847407452621"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14999847407452621"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14999847407452621"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14999847407452621"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0" tint="-0.14999847407452621"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14999847407452621"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14999847407452621"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14999847407452621"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="0" tint="-0.14999847407452621"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="0" tint="-0.14999847407452621"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -4220,9 +4269,9 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="Table Style 1" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="3" xr9:uid="{F44E0718-D341-4DA9-B15C-DFA5FBF475CB}">
-      <tableStyleElement type="wholeTable" dxfId="115"/>
-      <tableStyleElement type="headerRow" dxfId="114"/>
-      <tableStyleElement type="totalRow" dxfId="113"/>
+      <tableStyleElement type="wholeTable" dxfId="111"/>
+      <tableStyleElement type="headerRow" dxfId="110"/>
+      <tableStyleElement type="totalRow" dxfId="109"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -4387,7 +4436,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>GetBloombergDailyYieldCurve_cur!$F$2:$F$32</c:f>
+              <c:f>'Discount Rates'!$F$3:$F$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
@@ -4396,7 +4445,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>GetBloombergDailyYieldCurve_cur!$G$2:$G$32</c:f>
+              <c:f>'Discount Rates'!$G$3:$G$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
@@ -5185,6 +5234,10 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" fmlaLink="$D$35" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -5342,13 +5395,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>609599</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>561974</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5374,7 +5427,144 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>14494</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>99390</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>1030769</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>96076</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19457" name="Check Box 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s19457"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0F31715-3851-402D-BD22-D7C5BA22C6CB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>Freeze Current Rates</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="REPORT_OUTPUTS"/>
+      <sheetName val="Case Inputs"/>
+      <sheetName val="Base 1 PV Loss WLE"/>
+      <sheetName val="Base 1 PV Loss To Age"/>
+      <sheetName val="Base 2 PV Loss WLE"/>
+      <sheetName val="Base 2 PV Loss To Age"/>
+      <sheetName val="Base 3 PV Loss WLE"/>
+      <sheetName val="Base 3 PV Loss To Age"/>
+      <sheetName val="Credit 1 PV Loss WLE"/>
+      <sheetName val="Credit 1 PV Loss to Age"/>
+      <sheetName val="Credit 2 PV Loss WLE"/>
+      <sheetName val="Credit 2 PV Loss To Age"/>
+      <sheetName val="Discount Rates"/>
+      <sheetName val="LE_F"/>
+      <sheetName val="LE_M"/>
+      <sheetName val="WLE"/>
+      <sheetName val="CPI Data"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="ToggleBloombergRatesFreeze"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5528,13 +5718,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{0B4D98F6-F70F-984F-B70B-7A5DEB23520A}" name="Table18" displayName="Table18" ref="A2:D101" totalsRowShown="0" headerRowDxfId="112" headerRowBorderDxfId="111" tableBorderDxfId="110">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{0B4D98F6-F70F-984F-B70B-7A5DEB23520A}" name="Table18" displayName="Table18" ref="A2:D101" totalsRowShown="0" headerRowDxfId="108" headerRowBorderDxfId="107" tableBorderDxfId="106">
   <autoFilter ref="A2:D101" xr:uid="{C10D9EF0-FD23-48B8-93F2-AA9F47B7BA14}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{DE8B3259-05C9-C14B-8834-0A26F5DD5C08}" name="Variable Name" dataDxfId="109"/>
-    <tableColumn id="2" xr3:uid="{C88897C0-0B1B-D64F-B732-B0A2C2F73B6D}" name="Worksheet Name" dataDxfId="108"/>
-    <tableColumn id="3" xr3:uid="{7EE51D35-8D7C-214B-8BFF-57D8D765E7CD}" name="Cell Reference" dataDxfId="107"/>
-    <tableColumn id="4" xr3:uid="{D6B49E70-1CC5-C64B-8049-6EE43A46E18F}" name="Live Cell Value" dataDxfId="106">
+    <tableColumn id="1" xr3:uid="{DE8B3259-05C9-C14B-8834-0A26F5DD5C08}" name="Variable Name" dataDxfId="105"/>
+    <tableColumn id="2" xr3:uid="{C88897C0-0B1B-D64F-B732-B0A2C2F73B6D}" name="Worksheet Name" dataDxfId="104"/>
+    <tableColumn id="3" xr3:uid="{7EE51D35-8D7C-214B-8BFF-57D8D765E7CD}" name="Cell Reference" dataDxfId="103"/>
+    <tableColumn id="4" xr3:uid="{D6B49E70-1CC5-C64B-8049-6EE43A46E18F}" name="Live Cell Value" dataDxfId="102">
       <calculatedColumnFormula array="1">IF(OR(IF(OR(A3="", B3="", C3=""), "", INDIRECT("'" &amp; B3 &amp; "'!" &amp; C3))=0, IF(OR(A3="", B3="", C3=""), "", INDIRECT("'" &amp; B3 &amp; "'!" &amp; C3))=""),"",INDIRECT("'" &amp; B3 &amp; "'!" &amp; C3))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5543,32 +5733,32 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{04B72DAB-FFA8-4BF2-811F-CB4D286E2022}" name="PV_Summary_No_Rounding" displayName="PV_Summary_No_Rounding" ref="A1:G6" tableType="queryTable" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{04B72DAB-FFA8-4BF2-811F-CB4D286E2022}" name="PV_Summary_No_Rounding" displayName="PV_Summary_No_Rounding" ref="A1:G6" tableType="queryTable" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
   <autoFilter ref="A1:G6" xr:uid="{04B72DAB-FFA8-4BF2-811F-CB4D286E2022}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{C0195139-DAFB-4B19-891E-9841DB46068F}" uniqueName="1" name="RowType" queryTableFieldId="1" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{71DB2FC5-0689-4F86-A6B5-54437D3B175E}" uniqueName="2" name="CatSort" queryTableFieldId="2" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{F6C6AF8E-B196-4FFD-867C-A2806D72705B}" uniqueName="3" name="HeaderRank" queryTableFieldId="3" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{25637E68-D570-475A-8D61-6FA40C7EE9C7}" uniqueName="4" name="ITEM/SERVICE" queryTableFieldId="4" dataDxfId="41" dataCellStyle="Currency"/>
-    <tableColumn id="5" xr3:uid="{CD1DA0BA-7388-4850-809D-90ACEBF3DFDE}" uniqueName="5" name="LOWER" queryTableFieldId="5" dataDxfId="40" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{6B7869F7-699B-4C3E-AC03-338ECB282AEE}" uniqueName="6" name="MIDPOINT" queryTableFieldId="6" dataDxfId="39" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{4354290A-5001-49BF-98A8-AF11E800D126}" uniqueName="7" name="UPPER" queryTableFieldId="7" dataDxfId="38" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{C0195139-DAFB-4B19-891E-9841DB46068F}" uniqueName="1" name="RowType" queryTableFieldId="1" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{71DB2FC5-0689-4F86-A6B5-54437D3B175E}" uniqueName="2" name="CatSort" queryTableFieldId="2" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{F6C6AF8E-B196-4FFD-867C-A2806D72705B}" uniqueName="3" name="HeaderRank" queryTableFieldId="3" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{25637E68-D570-475A-8D61-6FA40C7EE9C7}" uniqueName="4" name="ITEM/SERVICE" queryTableFieldId="4" dataDxfId="37" dataCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{CD1DA0BA-7388-4850-809D-90ACEBF3DFDE}" uniqueName="5" name="LOWER" queryTableFieldId="5" dataDxfId="36" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{6B7869F7-699B-4C3E-AC03-338ECB282AEE}" uniqueName="6" name="MIDPOINT" queryTableFieldId="6" dataDxfId="35" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{4354290A-5001-49BF-98A8-AF11E800D126}" uniqueName="7" name="UPPER" queryTableFieldId="7" dataDxfId="34" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6E7C1877-99EE-49EC-9E2B-5081AD3741C3}" name="PV_Totals_By_Item" displayName="PV_Totals_By_Item" ref="A1:G6" tableType="queryTable" headerRowDxfId="37" dataDxfId="36" totalsRowDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6E7C1877-99EE-49EC-9E2B-5081AD3741C3}" name="PV_Totals_By_Item" displayName="PV_Totals_By_Item" ref="A1:G6" tableType="queryTable" headerRowDxfId="33" dataDxfId="32" totalsRowDxfId="31">
   <autoFilter ref="A1:G6" xr:uid="{6E7C1877-99EE-49EC-9E2B-5081AD3741C3}"/>
   <tableColumns count="7">
-    <tableColumn id="5" xr3:uid="{4B646FE9-BCFB-4A51-82F5-7E0DB7AE7849}" uniqueName="5" name="RowType" queryTableFieldId="28" dataDxfId="34" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{21F03B1B-B6AB-4F34-B622-776640B2EEC8}" uniqueName="6" name="CatSort" queryTableFieldId="29" dataDxfId="33" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{A7FBFC2B-1830-40DB-8412-8D8ABED10172}" uniqueName="7" name="HeaderRank" queryTableFieldId="30" dataDxfId="32" dataCellStyle="Currency"/>
-    <tableColumn id="1" xr3:uid="{F9F46062-182D-4AAA-8861-CEEAA03ADDBA}" uniqueName="1" name="ITEM/SERVICE" queryTableFieldId="24" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{EE2E4551-8EB5-44CB-AE92-07AF8F679061}" uniqueName="2" name="LOWER" queryTableFieldId="25" dataDxfId="29" totalsRowDxfId="28" dataCellStyle="Currency"/>
-    <tableColumn id="3" xr3:uid="{C3486620-2326-4D6A-BDD3-D3CEC5351208}" uniqueName="3" name="MIDPOINT" queryTableFieldId="26" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="Currency"/>
-    <tableColumn id="4" xr3:uid="{B6F4AE6F-7A5E-43F8-AF9A-0693CF4C0F30}" uniqueName="4" name="UPPER" totalsRowFunction="sum" queryTableFieldId="27" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{4B646FE9-BCFB-4A51-82F5-7E0DB7AE7849}" uniqueName="5" name="RowType" queryTableFieldId="28" dataDxfId="30" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{21F03B1B-B6AB-4F34-B622-776640B2EEC8}" uniqueName="6" name="CatSort" queryTableFieldId="29" dataDxfId="29" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{A7FBFC2B-1830-40DB-8412-8D8ABED10172}" uniqueName="7" name="HeaderRank" queryTableFieldId="30" dataDxfId="28" dataCellStyle="Currency"/>
+    <tableColumn id="1" xr3:uid="{F9F46062-182D-4AAA-8861-CEEAA03ADDBA}" uniqueName="1" name="ITEM/SERVICE" queryTableFieldId="24" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{EE2E4551-8EB5-44CB-AE92-07AF8F679061}" uniqueName="2" name="LOWER" queryTableFieldId="25" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Currency"/>
+    <tableColumn id="3" xr3:uid="{C3486620-2326-4D6A-BDD3-D3CEC5351208}" uniqueName="3" name="MIDPOINT" queryTableFieldId="26" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{B6F4AE6F-7A5E-43F8-AF9A-0693CF4C0F30}" uniqueName="4" name="UPPER" totalsRowFunction="sum" queryTableFieldId="27" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="Currency"/>
   </tableColumns>
   <tableStyleInfo name="Table Style 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5578,17 +5768,17 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0A0A7437-1EEB-4F0D-8AAA-C79C2C3D1F79}" name="Pivoted_By_Year" displayName="Pivoted_By_Year" ref="A1:K2" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:K2" xr:uid="{0A0A7437-1EEB-4F0D-8AAA-C79C2C3D1F79}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{0A77EAB7-D5C8-4327-A7AC-B3B7DD2E5766}" uniqueName="1" name="YearList" queryTableFieldId="1" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{AAD78A2C-03A7-46C3-8DFF-8198EECE1E75}" uniqueName="3" name="ItemKey (Low)" queryTableFieldId="4598" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{0A77EAB7-D5C8-4327-A7AC-B3B7DD2E5766}" uniqueName="1" name="YearList" queryTableFieldId="1" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{AAD78A2C-03A7-46C3-8DFF-8198EECE1E75}" uniqueName="3" name="ItemKey (Low)" queryTableFieldId="4598" dataDxfId="18"/>
     <tableColumn id="4" xr3:uid="{3DB04C61-78E9-4481-A307-3C799774432C}" uniqueName="4" name="Value (Low)" queryTableFieldId="4599"/>
     <tableColumn id="32" xr3:uid="{E11564CB-6398-4C55-B95C-37B9E3FC8B22}" uniqueName="32" name="Year Total (Low)" queryTableFieldId="39"/>
-    <tableColumn id="5" xr3:uid="{915072E0-D4A2-4D95-9B32-4F0D1D7CF2D2}" uniqueName="5" name="ItemKey (Mid)" queryTableFieldId="4600" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{915072E0-D4A2-4D95-9B32-4F0D1D7CF2D2}" uniqueName="5" name="ItemKey (Mid)" queryTableFieldId="4600" dataDxfId="17"/>
     <tableColumn id="6" xr3:uid="{428B8927-4240-4A74-B94F-DE06D564A2E0}" uniqueName="6" name="Value (Mid)" queryTableFieldId="4601"/>
     <tableColumn id="35" xr3:uid="{71CB6ADE-A970-474C-88C4-0F798F08C88D}" uniqueName="35" name="Year Total (Mid)" queryTableFieldId="42"/>
-    <tableColumn id="7" xr3:uid="{7A4E5DE6-66FF-4936-A48F-519A3DB1B0CE}" uniqueName="7" name="ItemKey (High)" queryTableFieldId="4602" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{7A4E5DE6-66FF-4936-A48F-519A3DB1B0CE}" uniqueName="7" name="ItemKey (High)" queryTableFieldId="4602" dataDxfId="16"/>
     <tableColumn id="8" xr3:uid="{3689BBFC-85A2-4C4B-8387-46E6CE3E46FE}" uniqueName="8" name="Value (High)" queryTableFieldId="4603"/>
     <tableColumn id="38" xr3:uid="{4CBF2134-17CC-4E3C-BE2E-4DB0900ECCC7}" uniqueName="38" name="Year Total (High)" queryTableFieldId="45"/>
-    <tableColumn id="2" xr3:uid="{DEC9B595-88D2-4018-8922-FD92A9226EBE}" uniqueName="2" name="Column1" queryTableFieldId="157" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{DEC9B595-88D2-4018-8922-FD92A9226EBE}" uniqueName="2" name="Column1" queryTableFieldId="157" dataDxfId="15">
       <calculatedColumnFormula>AVERAGE(Pivoted_By_Year[[#This Row],[Year Total (High)]],Pivoted_By_Year[[#This Row],[Year Total (Low)]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5608,82 +5798,71 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A3AB1506-1C62-4D21-9E0F-ABFD20A6F8C6}" name="GetBloombergDailyYieldCurve_cur_1" displayName="GetBloombergDailyYieldCurve_cur_1" ref="A1:C31" tableType="queryTable" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="A1:C31" xr:uid="{A3AB1506-1C62-4D21-9E0F-ABFD20A6F8C6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A3AB1506-1C62-4D21-9E0F-ABFD20A6F8C6}" name="GetBloombergDailyYieldCurve_cur_1" displayName="GetBloombergDailyYieldCurve_cur_1" ref="A2:C32" tableType="queryTable" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="A2:C32" xr:uid="{A3AB1506-1C62-4D21-9E0F-ABFD20A6F8C6}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{017DBA49-A675-4A2C-9D3A-5D218FE48C0E}" uniqueName="1" name="Year" queryTableFieldId="1" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{476B3F8B-5148-484F-94EA-C17412D817D4}" uniqueName="2" name="Time To Marity" queryTableFieldId="2" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{2E9DC6B9-284C-4F1D-89BF-F5F446B57AC0}" uniqueName="4" name="Discount Rate (Nominal)" queryTableFieldId="4" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{017DBA49-A675-4A2C-9D3A-5D218FE48C0E}" uniqueName="1" name="Year" queryTableFieldId="1" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{476B3F8B-5148-484F-94EA-C17412D817D4}" uniqueName="2" name="Time To Marity" queryTableFieldId="2" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{2E9DC6B9-284C-4F1D-89BF-F5F446B57AC0}" uniqueName="4" name="Discount Rate (Nominal)" queryTableFieldId="4" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{32BFE16E-A259-4C63-8DCF-00C9A6EFA78D}" name="Table15" displayName="Table15" ref="F1:G32" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="F1:G32" xr:uid="{32BFE16E-A259-4C63-8DCF-00C9A6EFA78D}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{099144D5-37E0-4580-8BDC-BF9DA5901655}" name="PASTED YEAR" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{DEBA212E-45CC-4A41-A95A-1A261BC6D9AB}" name="PASTED DISCOUNT RATES" dataDxfId="10"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ItemInputs" displayName="ItemInputs" ref="A1:O55" totalsRowCount="1" headerRowDxfId="105" dataDxfId="104" totalsRowDxfId="103">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ItemInputs" displayName="ItemInputs" ref="A1:O55" totalsRowCount="1" headerRowDxfId="101" dataDxfId="100" totalsRowDxfId="99">
   <autoFilter ref="A1:O54" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Item Name" dataDxfId="102" totalsRowDxfId="101"/>
-    <tableColumn id="13" xr3:uid="{69586349-5A6C-4C48-BCB1-5C8A5322D0D3}" name="ItemKey" dataDxfId="100" totalsRowDxfId="99">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Item Name" dataDxfId="98" totalsRowDxfId="97"/>
+    <tableColumn id="13" xr3:uid="{69586349-5A6C-4C48-BCB1-5C8A5322D0D3}" name="ItemKey" dataDxfId="96" totalsRowDxfId="95">
       <calculatedColumnFormula>ItemInputs[[#This Row],[Item Name]] &amp; " (" &amp; ItemInputs[[#This Row],[Sort Order]] &amp; ")"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{0C697847-13AA-4117-955F-38AEE7F2D509}" name="Category" dataDxfId="98" totalsRowDxfId="97"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start Year" dataDxfId="96" totalsRowDxfId="95"/>
-    <tableColumn id="15" xr3:uid="{5E7EFE17-AC27-4775-8CCB-970D86383EBC}" name="Start Offset (Years)" dataDxfId="94" totalsRowDxfId="93"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Duration" dataDxfId="92" totalsRowDxfId="91"/>
-    <tableColumn id="12" xr3:uid="{11331C1E-E934-4A8E-9BD9-32983E09B998}" name="InitialCostLow" totalsRowFunction="sum" dataDxfId="90" totalsRowDxfId="89"/>
-    <tableColumn id="9" xr3:uid="{4312D196-F952-45D8-8741-437FA528B4CA}" name="InitialCostHigh" totalsRowFunction="sum" dataDxfId="88" totalsRowDxfId="87"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Low Cost per Use" totalsRowFunction="sum" dataDxfId="86" totalsRowDxfId="85"/>
-    <tableColumn id="11" xr3:uid="{DD77257E-FAE9-4D41-827D-7595596F9F01}" name="High Cost per Use" totalsRowFunction="sum" dataDxfId="84" totalsRowDxfId="83"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Frequency" dataDxfId="82" totalsRowDxfId="81"/>
-    <tableColumn id="7" xr3:uid="{0CBD786F-1716-4E4E-861E-B4051F17796E}" name="Interval (Years)" dataDxfId="80" totalsRowDxfId="79"/>
-    <tableColumn id="10" xr3:uid="{25282397-8296-490A-B301-5F98E9B69B45}" name="Sort Order" dataDxfId="78" totalsRowDxfId="77"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Growth" dataDxfId="76" totalsRowDxfId="75"/>
-    <tableColumn id="8" xr3:uid="{DEF69107-78BD-43AA-948E-950FA8C9B6D6}" name="CostType" dataDxfId="74" totalsRowDxfId="73"/>
+    <tableColumn id="14" xr3:uid="{0C697847-13AA-4117-955F-38AEE7F2D509}" name="Category" dataDxfId="94" totalsRowDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start Year" dataDxfId="92" totalsRowDxfId="91"/>
+    <tableColumn id="15" xr3:uid="{5E7EFE17-AC27-4775-8CCB-970D86383EBC}" name="Start Offset (Years)" dataDxfId="90" totalsRowDxfId="89"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Duration" dataDxfId="88" totalsRowDxfId="87"/>
+    <tableColumn id="12" xr3:uid="{11331C1E-E934-4A8E-9BD9-32983E09B998}" name="InitialCostLow" totalsRowFunction="sum" dataDxfId="86" totalsRowDxfId="85"/>
+    <tableColumn id="9" xr3:uid="{4312D196-F952-45D8-8741-437FA528B4CA}" name="InitialCostHigh" totalsRowFunction="sum" dataDxfId="84" totalsRowDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Low Cost per Use" totalsRowFunction="sum" dataDxfId="82" totalsRowDxfId="81"/>
+    <tableColumn id="11" xr3:uid="{DD77257E-FAE9-4D41-827D-7595596F9F01}" name="High Cost per Use" totalsRowFunction="sum" dataDxfId="80" totalsRowDxfId="79"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Frequency" dataDxfId="78" totalsRowDxfId="77"/>
+    <tableColumn id="7" xr3:uid="{0CBD786F-1716-4E4E-861E-B4051F17796E}" name="Interval (Years)" dataDxfId="76" totalsRowDxfId="75"/>
+    <tableColumn id="10" xr3:uid="{25282397-8296-490A-B301-5F98E9B69B45}" name="Sort Order" dataDxfId="74" totalsRowDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Growth" dataDxfId="72" totalsRowDxfId="71"/>
+    <tableColumn id="8" xr3:uid="{DEF69107-78BD-43AA-948E-950FA8C9B6D6}" name="CostType" dataDxfId="70" totalsRowDxfId="69"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7914EDB0-A692-4509-9B14-CBA25587C27C}" name="DiscountRateDefaults" displayName="DiscountRateDefaults" ref="A1:B3" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7914EDB0-A692-4509-9B14-CBA25587C27C}" name="DiscountRateDefaults" displayName="DiscountRateDefaults" ref="A1:B3" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
   <autoFilter ref="A1:B3" xr:uid="{7914EDB0-A692-4509-9B14-CBA25587C27C}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7B5CB263-8595-47BB-9B83-A136D870840A}" name="Setting" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{252EFA06-D044-48FF-AD5F-AD7217789FA2}" name="Value" dataDxfId="69"/>
+    <tableColumn id="1" xr3:uid="{7B5CB263-8595-47BB-9B83-A136D870840A}" name="Setting" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{252EFA06-D044-48FF-AD5F-AD7217789FA2}" name="Value" dataDxfId="65"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{A50B493A-AB6F-4FE2-A4D8-4ED87E71424C}" name="OptionsTable" displayName="OptionsTable" ref="A5:B13" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{A50B493A-AB6F-4FE2-A4D8-4ED87E71424C}" name="OptionsTable" displayName="OptionsTable" ref="A5:B13" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
   <autoFilter ref="A5:B13" xr:uid="{A50B493A-AB6F-4FE2-A4D8-4ED87E71424C}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{454320BB-D2B2-4D0A-B712-14824B86607B}" name="Option Name" dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{E25BE358-872F-4B95-8C86-8802A909B822}" name="Value" dataDxfId="65"/>
+    <tableColumn id="1" xr3:uid="{454320BB-D2B2-4D0A-B712-14824B86607B}" name="Option Name" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{E25BE358-872F-4B95-8C86-8802A909B822}" name="Value" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{89F53BAA-F43D-4D75-8A4E-57A0DEB36107}" name="Table11" displayName="Table11" ref="G1:H2" insertRow="1" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{89F53BAA-F43D-4D75-8A4E-57A0DEB36107}" name="Table11" displayName="Table11" ref="G1:H2" insertRow="1" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
   <autoFilter ref="G1:H2" xr:uid="{89F53BAA-F43D-4D75-8A4E-57A0DEB36107}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E9BC6FF2-8327-4755-81CC-187A8A29442E}" name="Year" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{F1B0F7A0-9E8A-4722-B481-F03CDF78FF2D}" name="Discount Rate (Nominal)" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{E9BC6FF2-8327-4755-81CC-187A8A29442E}" name="Year" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{F1B0F7A0-9E8A-4722-B481-F03CDF78FF2D}" name="Discount Rate (Nominal)" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5749,15 +5928,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{D9756F7E-4136-42C2-969A-EFE5ACC68CEB}" name="DepletionOfFunds" displayName="DepletionOfFunds" ref="A1:O59" totalsRowShown="0">
   <autoFilter ref="A1:O59" xr:uid="{D9756F7E-4136-42C2-969A-EFE5ACC68CEB}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{53EE76AD-A0DA-482F-9B3E-B5C94A79DE1C}" name="YearList" dataDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{BEE39F59-A19A-4844-AB3B-F69CCBBE3CB8}" name="TotalCostLow" dataDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{D3EAF15D-8A8A-454E-98CD-7D8BB727F07A}" name="TotalCostMid" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{68B5591D-987C-42D5-AEBB-07D0120DED7D}" name="TotalCostHigh" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{53EE76AD-A0DA-482F-9B3E-B5C94A79DE1C}" name="YearList" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{BEE39F59-A19A-4844-AB3B-F69CCBBE3CB8}" name="TotalCostLow" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{D3EAF15D-8A8A-454E-98CD-7D8BB727F07A}" name="TotalCostMid" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{68B5591D-987C-42D5-AEBB-07D0120DED7D}" name="TotalCostHigh" dataDxfId="53"/>
     <tableColumn id="5" xr3:uid="{56DC093C-17AE-4859-BF59-5E7B3DE611DC}" name="AdjustedRate"/>
-    <tableColumn id="6" xr3:uid="{A00483D8-9CC1-4FB1-ADEF-E9FB090DEB45}" name="AdjRate" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{2CEB2B29-6B74-4E8E-B933-B2F833E5C50E}" name="PV_Low" dataDxfId="55"/>
-    <tableColumn id="8" xr3:uid="{90A022E3-0BF8-4BEC-A762-CEC2DD854641}" name="PV_Mid" dataDxfId="54"/>
-    <tableColumn id="9" xr3:uid="{9B568AFC-0A6F-4559-9198-C71A6C0BCEBC}" name="PV_High" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{A00483D8-9CC1-4FB1-ADEF-E9FB090DEB45}" name="AdjRate" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{2CEB2B29-6B74-4E8E-B933-B2F833E5C50E}" name="PV_Low" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{90A022E3-0BF8-4BEC-A762-CEC2DD854641}" name="PV_Mid" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{9B568AFC-0A6F-4559-9198-C71A6C0BCEBC}" name="PV_High" dataDxfId="49"/>
     <tableColumn id="10" xr3:uid="{2A9D90BA-9C43-4197-A627-89E8EDA7D352}" name="FundBefore_Low"/>
     <tableColumn id="11" xr3:uid="{110136F3-0482-45A7-8DC8-8B9F1BEE33B3}" name="FundAfter_Low"/>
     <tableColumn id="12" xr3:uid="{D215DC6C-4431-43E0-BE87-B061A096B0CA}" name="FundBefore_Mid"/>
@@ -5770,7 +5949,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{363C6C6C-0A2B-4C8D-9FCF-448FA8276BEE}" name="Future_Cost_By_Year" displayName="Future_Cost_By_Year" ref="A1:D17" tableType="queryTable" totalsRowShown="0" headerRowDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{363C6C6C-0A2B-4C8D-9FCF-448FA8276BEE}" name="Future_Cost_By_Year" displayName="Future_Cost_By_Year" ref="A1:D17" tableType="queryTable" totalsRowShown="0" headerRowDxfId="48">
   <autoFilter ref="A1:D17" xr:uid="{363C6C6C-0A2B-4C8D-9FCF-448FA8276BEE}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{AF325518-2E66-4DEE-BD2D-B19618EC5CAA}" uniqueName="1" name="YearList" queryTableFieldId="1"/>
@@ -5783,12 +5962,12 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{4E875877-9580-437F-888D-2345B7BB85DD}" name="CustomDiscountCurve" displayName="CustomDiscountCurve" ref="A1:C37" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{4E875877-9580-437F-888D-2345B7BB85DD}" name="CustomDiscountCurve" displayName="CustomDiscountCurve" ref="A1:C37" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="A1:C37" xr:uid="{4E875877-9580-437F-888D-2345B7BB85DD}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{DB055912-AF2D-4BCD-AEE5-BE6F46DA8D7C}" name="Year" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{E592388B-A21E-4BE9-ACC6-A7E7F25B1CEE}" name="Discount Rate (Nominal)" dataDxfId="48"/>
-    <tableColumn id="3" xr3:uid="{01343765-9C51-433B-8C62-967D1D5154EB}" name="%Rate" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{DB055912-AF2D-4BCD-AEE5-BE6F46DA8D7C}" name="Year" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{E592388B-A21E-4BE9-ACC6-A7E7F25B1CEE}" name="Discount Rate (Nominal)" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{01343765-9C51-433B-8C62-967D1D5154EB}" name="%Rate" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6087,7 +6266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D316C85F-EFED-8843-8781-213AEBA50528}">
-  <sheetPr>
+  <sheetPr codeName="Sheet9">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:J101"/>
@@ -6241,7 +6420,7 @@
         <v>324</v>
       </c>
       <c r="C7" s="72" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D7" s="82" cm="1">
         <f t="array" aca="1" ref="D7" ca="1">IF(OR(IF(OR(A7="", B7="", C7=""), "", INDIRECT("'" &amp; B7 &amp; "'!" &amp; C7))=0, IF(OR(A7="", B7="", C7=""), "", INDIRECT("'" &amp; B7 &amp; "'!" &amp; C7))=""),"",INDIRECT("'" &amp; B7 &amp; "'!" &amp; C7))</f>
@@ -6260,7 +6439,7 @@
         <v>324</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D8" s="82" t="str" cm="1">
         <f t="array" aca="1" ref="D8" ca="1">IF(OR(IF(OR(A8="", B8="", C8=""), "", INDIRECT("'" &amp; B8 &amp; "'!" &amp; C8))=0, IF(OR(A8="", B8="", C8=""), "", INDIRECT("'" &amp; B8 &amp; "'!" &amp; C8))=""),"",INDIRECT("'" &amp; B8 &amp; "'!" &amp; C8))</f>
@@ -6279,7 +6458,7 @@
         <v>324</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D9" s="103" cm="1">
         <f t="array" aca="1" ref="D9" ca="1">IF(OR(IF(OR(A9="", B9="", C9=""), "", INDIRECT("'" &amp; B9 &amp; "'!" &amp; C9))=0, IF(OR(A9="", B9="", C9=""), "", INDIRECT("'" &amp; B9 &amp; "'!" &amp; C9))=""),"",INDIRECT("'" &amp; B9 &amp; "'!" &amp; C9))</f>
@@ -6298,7 +6477,7 @@
         <v>324</v>
       </c>
       <c r="C10" s="105" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D10" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D10" ca="1">IF(OR(IF(OR(A10="", B10="", C10=""), "", INDIRECT("'" &amp; B10 &amp; "'!" &amp; C10))=0, IF(OR(A10="", B10="", C10=""), "", INDIRECT("'" &amp; B10 &amp; "'!" &amp; C10))=""),"",INDIRECT("'" &amp; B10 &amp; "'!" &amp; C10))</f>
@@ -6317,7 +6496,7 @@
         <v>324</v>
       </c>
       <c r="C11" s="105" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D11" s="103" cm="1">
         <f t="array" aca="1" ref="D11" ca="1">IF(OR(IF(OR(A11="", B11="", C11=""), "", INDIRECT("'" &amp; B11 &amp; "'!" &amp; C11))=0, IF(OR(A11="", B11="", C11=""), "", INDIRECT("'" &amp; B11 &amp; "'!" &amp; C11))=""),"",INDIRECT("'" &amp; B11 &amp; "'!" &amp; C11))</f>
@@ -6336,7 +6515,7 @@
         <v>324</v>
       </c>
       <c r="C12" s="105" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D12" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D12" ca="1">IF(OR(IF(OR(A12="", B12="", C12=""), "", INDIRECT("'" &amp; B12 &amp; "'!" &amp; C12))=0, IF(OR(A12="", B12="", C12=""), "", INDIRECT("'" &amp; B12 &amp; "'!" &amp; C12))=""),"",INDIRECT("'" &amp; B12 &amp; "'!" &amp; C12))</f>
@@ -6355,7 +6534,7 @@
         <v>324</v>
       </c>
       <c r="C13" s="105" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D13" s="103" cm="1">
         <f t="array" aca="1" ref="D13" ca="1">IF(OR(IF(OR(A13="", B13="", C13=""), "", INDIRECT("'" &amp; B13 &amp; "'!" &amp; C13))=0, IF(OR(A13="", B13="", C13=""), "", INDIRECT("'" &amp; B13 &amp; "'!" &amp; C13))=""),"",INDIRECT("'" &amp; B13 &amp; "'!" &amp; C13))</f>
@@ -6374,7 +6553,7 @@
         <v>324</v>
       </c>
       <c r="C14" s="105" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D14" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D14" ca="1">IF(OR(IF(OR(A14="", B14="", C14=""), "", INDIRECT("'" &amp; B14 &amp; "'!" &amp; C14))=0, IF(OR(A14="", B14="", C14=""), "", INDIRECT("'" &amp; B14 &amp; "'!" &amp; C14))=""),"",INDIRECT("'" &amp; B14 &amp; "'!" &amp; C14))</f>
@@ -6393,7 +6572,7 @@
         <v>324</v>
       </c>
       <c r="C15" s="105" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D15" s="103" cm="1">
         <f t="array" aca="1" ref="D15" ca="1">IF(OR(IF(OR(A15="", B15="", C15=""), "", INDIRECT("'" &amp; B15 &amp; "'!" &amp; C15))=0, IF(OR(A15="", B15="", C15=""), "", INDIRECT("'" &amp; B15 &amp; "'!" &amp; C15))=""),"",INDIRECT("'" &amp; B15 &amp; "'!" &amp; C15))</f>
@@ -6412,7 +6591,7 @@
         <v>324</v>
       </c>
       <c r="C16" s="105" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D16" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D16" ca="1">IF(OR(IF(OR(A16="", B16="", C16=""), "", INDIRECT("'" &amp; B16 &amp; "'!" &amp; C16))=0, IF(OR(A16="", B16="", C16=""), "", INDIRECT("'" &amp; B16 &amp; "'!" &amp; C16))=""),"",INDIRECT("'" &amp; B16 &amp; "'!" &amp; C16))</f>
@@ -6431,7 +6610,7 @@
         <v>324</v>
       </c>
       <c r="C17" s="105" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D17" s="103" cm="1">
         <f t="array" aca="1" ref="D17" ca="1">IF(OR(IF(OR(A17="", B17="", C17=""), "", INDIRECT("'" &amp; B17 &amp; "'!" &amp; C17))=0, IF(OR(A17="", B17="", C17=""), "", INDIRECT("'" &amp; B17 &amp; "'!" &amp; C17))=""),"",INDIRECT("'" &amp; B17 &amp; "'!" &amp; C17))</f>
@@ -6450,7 +6629,7 @@
         <v>324</v>
       </c>
       <c r="C18" s="105" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D18" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D18" ca="1">IF(OR(IF(OR(A18="", B18="", C18=""), "", INDIRECT("'" &amp; B18 &amp; "'!" &amp; C18))=0, IF(OR(A18="", B18="", C18=""), "", INDIRECT("'" &amp; B18 &amp; "'!" &amp; C18))=""),"",INDIRECT("'" &amp; B18 &amp; "'!" &amp; C18))</f>
@@ -6469,7 +6648,7 @@
         <v>324</v>
       </c>
       <c r="C19" s="105" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D19" s="103" cm="1">
         <f t="array" aca="1" ref="D19" ca="1">IF(OR(IF(OR(A19="", B19="", C19=""), "", INDIRECT("'" &amp; B19 &amp; "'!" &amp; C19))=0, IF(OR(A19="", B19="", C19=""), "", INDIRECT("'" &amp; B19 &amp; "'!" &amp; C19))=""),"",INDIRECT("'" &amp; B19 &amp; "'!" &amp; C19))</f>
@@ -6488,7 +6667,7 @@
         <v>324</v>
       </c>
       <c r="C20" s="105" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D20" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D20" ca="1">IF(OR(IF(OR(A20="", B20="", C20=""), "", INDIRECT("'" &amp; B20 &amp; "'!" &amp; C20))=0, IF(OR(A20="", B20="", C20=""), "", INDIRECT("'" &amp; B20 &amp; "'!" &amp; C20))=""),"",INDIRECT("'" &amp; B20 &amp; "'!" &amp; C20))</f>
@@ -6507,7 +6686,7 @@
         <v>324</v>
       </c>
       <c r="C21" s="105" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D21" s="103" cm="1">
         <f t="array" aca="1" ref="D21" ca="1">IF(OR(IF(OR(A21="", B21="", C21=""), "", INDIRECT("'" &amp; B21 &amp; "'!" &amp; C21))=0, IF(OR(A21="", B21="", C21=""), "", INDIRECT("'" &amp; B21 &amp; "'!" &amp; C21))=""),"",INDIRECT("'" &amp; B21 &amp; "'!" &amp; C21))</f>
@@ -6526,7 +6705,7 @@
         <v>324</v>
       </c>
       <c r="C22" s="105" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D22" s="103" t="str" cm="1">
         <f t="array" aca="1" ref="D22" ca="1">IF(OR(IF(OR(A22="", B22="", C22=""), "", INDIRECT("'" &amp; B22 &amp; "'!" &amp; C22))=0, IF(OR(A22="", B22="", C22=""), "", INDIRECT("'" &amp; B22 &amp; "'!" &amp; C22))=""),"",INDIRECT("'" &amp; B22 &amp; "'!" &amp; C22))</f>
@@ -6545,7 +6724,7 @@
         <v>324</v>
       </c>
       <c r="C23" s="105" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D23" s="103" cm="1">
         <f t="array" aca="1" ref="D23" ca="1">IF(OR(IF(OR(A23="", B23="", C23=""), "", INDIRECT("'" &amp; B23 &amp; "'!" &amp; C23))=0, IF(OR(A23="", B23="", C23=""), "", INDIRECT("'" &amp; B23 &amp; "'!" &amp; C23))=""),"",INDIRECT("'" &amp; B23 &amp; "'!" &amp; C23))</f>
@@ -6564,7 +6743,7 @@
         <v>324</v>
       </c>
       <c r="C24" s="65" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D24" s="82" t="str" cm="1">
         <f t="array" aca="1" ref="D24" ca="1">IF(OR(IF(OR(A24="", B24="", C24=""), "", INDIRECT("'" &amp; B24 &amp; "'!" &amp; C24))=0, IF(OR(A24="", B24="", C24=""), "", INDIRECT("'" &amp; B24 &amp; "'!" &amp; C24))=""),"",INDIRECT("'" &amp; B24 &amp; "'!" &amp; C24))</f>
@@ -6583,7 +6762,7 @@
         <v>324</v>
       </c>
       <c r="C25" s="72" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D25" s="82" cm="1">
         <f t="array" aca="1" ref="D25" ca="1">IF(OR(IF(OR(A25="", B25="", C25=""), "", INDIRECT("'" &amp; B25 &amp; "'!" &amp; C25))=0, IF(OR(A25="", B25="", C25=""), "", INDIRECT("'" &amp; B25 &amp; "'!" &amp; C25))=""),"",INDIRECT("'" &amp; B25 &amp; "'!" &amp; C25))</f>
@@ -6602,7 +6781,7 @@
         <v>324</v>
       </c>
       <c r="C26" s="72" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D26" s="82" t="str" cm="1">
         <f t="array" aca="1" ref="D26" ca="1">IF(OR(IF(OR(A26="", B26="", C26=""), "", INDIRECT("'" &amp; B26 &amp; "'!" &amp; C26))=0, IF(OR(A26="", B26="", C26=""), "", INDIRECT("'" &amp; B26 &amp; "'!" &amp; C26))=""),"",INDIRECT("'" &amp; B26 &amp; "'!" &amp; C26))</f>
@@ -6623,9 +6802,9 @@
       <c r="C27" s="72" t="s">
         <v>345</v>
       </c>
-      <c r="D27" s="83" t="str" cm="1">
+      <c r="D27" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D27" ca="1">IF(OR(IF(OR(A27="", B27="", C27=""), "", INDIRECT("'" &amp; B27 &amp; "'!" &amp; C27))=0, IF(OR(A27="", B27="", C27=""), "", INDIRECT("'" &amp; B27 &amp; "'!" &amp; C27))=""),"",INDIRECT("'" &amp; B27 &amp; "'!" &amp; C27))</f>
-        <v>2.133</v>
+        <v>#REF!</v>
       </c>
       <c r="F27" s="77"/>
       <c r="G27" s="78"/>
@@ -6642,9 +6821,9 @@
       <c r="C28" s="72" t="s">
         <v>347</v>
       </c>
-      <c r="D28" s="83" t="str" cm="1">
+      <c r="D28" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D28" ca="1">IF(OR(IF(OR(A28="", B28="", C28=""), "", INDIRECT("'" &amp; B28 &amp; "'!" &amp; C28))=0, IF(OR(A28="", B28="", C28=""), "", INDIRECT("'" &amp; B28 &amp; "'!" &amp; C28))=""),"",INDIRECT("'" &amp; B28 &amp; "'!" &amp; C28))</f>
-        <v>2.106</v>
+        <v>#REF!</v>
       </c>
       <c r="F28" s="73"/>
       <c r="G28" s="74"/>
@@ -6661,9 +6840,9 @@
       <c r="C29" s="72" t="s">
         <v>349</v>
       </c>
-      <c r="D29" s="83" t="str" cm="1">
+      <c r="D29" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D29" ca="1">IF(OR(IF(OR(A29="", B29="", C29=""), "", INDIRECT("'" &amp; B29 &amp; "'!" &amp; C29))=0, IF(OR(A29="", B29="", C29=""), "", INDIRECT("'" &amp; B29 &amp; "'!" &amp; C29))=""),"",INDIRECT("'" &amp; B29 &amp; "'!" &amp; C29))</f>
-        <v>2.098</v>
+        <v>#REF!</v>
       </c>
       <c r="F29" s="77"/>
       <c r="G29" s="78"/>
@@ -6680,9 +6859,9 @@
       <c r="C30" s="72" t="s">
         <v>351</v>
       </c>
-      <c r="D30" s="83" t="str" cm="1">
+      <c r="D30" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D30" ca="1">IF(OR(IF(OR(A30="", B30="", C30=""), "", INDIRECT("'" &amp; B30 &amp; "'!" &amp; C30))=0, IF(OR(A30="", B30="", C30=""), "", INDIRECT("'" &amp; B30 &amp; "'!" &amp; C30))=""),"",INDIRECT("'" &amp; B30 &amp; "'!" &amp; C30))</f>
-        <v>2.124</v>
+        <v>#REF!</v>
       </c>
       <c r="F30" s="73"/>
       <c r="G30" s="74"/>
@@ -6700,9 +6879,9 @@
       <c r="C31" s="72" t="s">
         <v>352</v>
       </c>
-      <c r="D31" s="83" t="str" cm="1">
+      <c r="D31" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D31" ca="1">IF(OR(IF(OR(A31="", B31="", C31=""), "", INDIRECT("'" &amp; B31 &amp; "'!" &amp; C31))=0, IF(OR(A31="", B31="", C31=""), "", INDIRECT("'" &amp; B31 &amp; "'!" &amp; C31))=""),"",INDIRECT("'" &amp; B31 &amp; "'!" &amp; C31))</f>
-        <v>2.157</v>
+        <v>#REF!</v>
       </c>
       <c r="F31" s="77"/>
       <c r="G31" s="78"/>
@@ -6720,9 +6899,9 @@
       <c r="C32" s="72" t="s">
         <v>353</v>
       </c>
-      <c r="D32" s="83" t="str" cm="1">
+      <c r="D32" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D32" ca="1">IF(OR(IF(OR(A32="", B32="", C32=""), "", INDIRECT("'" &amp; B32 &amp; "'!" &amp; C32))=0, IF(OR(A32="", B32="", C32=""), "", INDIRECT("'" &amp; B32 &amp; "'!" &amp; C32))=""),"",INDIRECT("'" &amp; B32 &amp; "'!" &amp; C32))</f>
-        <v>2.216</v>
+        <v>#REF!</v>
       </c>
       <c r="F32" s="73"/>
       <c r="G32" s="74"/>
@@ -6740,9 +6919,9 @@
       <c r="C33" s="72" t="s">
         <v>354</v>
       </c>
-      <c r="D33" s="83" t="str" cm="1">
+      <c r="D33" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D33" ca="1">IF(OR(IF(OR(A33="", B33="", C33=""), "", INDIRECT("'" &amp; B33 &amp; "'!" &amp; C33))=0, IF(OR(A33="", B33="", C33=""), "", INDIRECT("'" &amp; B33 &amp; "'!" &amp; C33))=""),"",INDIRECT("'" &amp; B33 &amp; "'!" &amp; C33))</f>
-        <v>2.309</v>
+        <v>#REF!</v>
       </c>
       <c r="F33" s="77"/>
       <c r="G33" s="78"/>
@@ -6760,9 +6939,9 @@
       <c r="C34" s="72" t="s">
         <v>355</v>
       </c>
-      <c r="D34" s="83" t="str" cm="1">
+      <c r="D34" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D34" ca="1">IF(OR(IF(OR(A34="", B34="", C34=""), "", INDIRECT("'" &amp; B34 &amp; "'!" &amp; C34))=0, IF(OR(A34="", B34="", C34=""), "", INDIRECT("'" &amp; B34 &amp; "'!" &amp; C34))=""),"",INDIRECT("'" &amp; B34 &amp; "'!" &amp; C34))</f>
-        <v>2.353</v>
+        <v>#REF!</v>
       </c>
       <c r="F34" s="73"/>
       <c r="G34" s="74"/>
@@ -6780,9 +6959,9 @@
       <c r="C35" s="72" t="s">
         <v>356</v>
       </c>
-      <c r="D35" s="83" t="str" cm="1">
+      <c r="D35" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D35" ca="1">IF(OR(IF(OR(A35="", B35="", C35=""), "", INDIRECT("'" &amp; B35 &amp; "'!" &amp; C35))=0, IF(OR(A35="", B35="", C35=""), "", INDIRECT("'" &amp; B35 &amp; "'!" &amp; C35))=""),"",INDIRECT("'" &amp; B35 &amp; "'!" &amp; C35))</f>
-        <v>2.456</v>
+        <v>#REF!</v>
       </c>
       <c r="F35" s="77"/>
       <c r="G35" s="78"/>
@@ -6800,9 +6979,9 @@
       <c r="C36" s="72" t="s">
         <v>357</v>
       </c>
-      <c r="D36" s="83" t="str" cm="1">
+      <c r="D36" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D36" ca="1">IF(OR(IF(OR(A36="", B36="", C36=""), "", INDIRECT("'" &amp; B36 &amp; "'!" &amp; C36))=0, IF(OR(A36="", B36="", C36=""), "", INDIRECT("'" &amp; B36 &amp; "'!" &amp; C36))=""),"",INDIRECT("'" &amp; B36 &amp; "'!" &amp; C36))</f>
-        <v>2.574</v>
+        <v>#REF!</v>
       </c>
       <c r="F36" s="73"/>
       <c r="G36" s="74"/>
@@ -6820,9 +6999,9 @@
       <c r="C37" s="72" t="s">
         <v>358</v>
       </c>
-      <c r="D37" s="83" t="str" cm="1">
+      <c r="D37" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D37" ca="1">IF(OR(IF(OR(A37="", B37="", C37=""), "", INDIRECT("'" &amp; B37 &amp; "'!" &amp; C37))=0, IF(OR(A37="", B37="", C37=""), "", INDIRECT("'" &amp; B37 &amp; "'!" &amp; C37))=""),"",INDIRECT("'" &amp; B37 &amp; "'!" &amp; C37))</f>
-        <v>2.698</v>
+        <v>#REF!</v>
       </c>
       <c r="F37" s="77"/>
       <c r="G37" s="78"/>
@@ -6840,9 +7019,9 @@
       <c r="C38" s="72" t="s">
         <v>359</v>
       </c>
-      <c r="D38" s="83" t="str" cm="1">
+      <c r="D38" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D38" ca="1">IF(OR(IF(OR(A38="", B38="", C38=""), "", INDIRECT("'" &amp; B38 &amp; "'!" &amp; C38))=0, IF(OR(A38="", B38="", C38=""), "", INDIRECT("'" &amp; B38 &amp; "'!" &amp; C38))=""),"",INDIRECT("'" &amp; B38 &amp; "'!" &amp; C38))</f>
-        <v>2.815</v>
+        <v>#REF!</v>
       </c>
       <c r="F38" s="73"/>
       <c r="G38" s="74"/>
@@ -6860,9 +7039,9 @@
       <c r="C39" s="72" t="s">
         <v>360</v>
       </c>
-      <c r="D39" s="83" t="str" cm="1">
+      <c r="D39" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D39" ca="1">IF(OR(IF(OR(A39="", B39="", C39=""), "", INDIRECT("'" &amp; B39 &amp; "'!" &amp; C39))=0, IF(OR(A39="", B39="", C39=""), "", INDIRECT("'" &amp; B39 &amp; "'!" &amp; C39))=""),"",INDIRECT("'" &amp; B39 &amp; "'!" &amp; C39))</f>
-        <v>2.905</v>
+        <v>#REF!</v>
       </c>
       <c r="F39" s="77"/>
       <c r="G39" s="78"/>
@@ -6880,9 +7059,9 @@
       <c r="C40" s="72" t="s">
         <v>361</v>
       </c>
-      <c r="D40" s="83" t="str" cm="1">
+      <c r="D40" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D40" ca="1">IF(OR(IF(OR(A40="", B40="", C40=""), "", INDIRECT("'" &amp; B40 &amp; "'!" &amp; C40))=0, IF(OR(A40="", B40="", C40=""), "", INDIRECT("'" &amp; B40 &amp; "'!" &amp; C40))=""),"",INDIRECT("'" &amp; B40 &amp; "'!" &amp; C40))</f>
-        <v>3.034</v>
+        <v>#REF!</v>
       </c>
       <c r="F40" s="84"/>
       <c r="G40" s="85"/>
@@ -6900,9 +7079,9 @@
       <c r="C41" s="72" t="s">
         <v>362</v>
       </c>
-      <c r="D41" s="83" t="str" cm="1">
+      <c r="D41" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D41" ca="1">IF(OR(IF(OR(A41="", B41="", C41=""), "", INDIRECT("'" &amp; B41 &amp; "'!" &amp; C41))=0, IF(OR(A41="", B41="", C41=""), "", INDIRECT("'" &amp; B41 &amp; "'!" &amp; C41))=""),"",INDIRECT("'" &amp; B41 &amp; "'!" &amp; C41))</f>
-        <v>3.153</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -6916,9 +7095,9 @@
       <c r="C42" s="72" t="s">
         <v>363</v>
       </c>
-      <c r="D42" s="83" t="str" cm="1">
+      <c r="D42" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D42" ca="1">IF(OR(IF(OR(A42="", B42="", C42=""), "", INDIRECT("'" &amp; B42 &amp; "'!" &amp; C42))=0, IF(OR(A42="", B42="", C42=""), "", INDIRECT("'" &amp; B42 &amp; "'!" &amp; C42))=""),"",INDIRECT("'" &amp; B42 &amp; "'!" &amp; C42))</f>
-        <v>3.306</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -6932,9 +7111,9 @@
       <c r="C43" s="72" t="s">
         <v>364</v>
       </c>
-      <c r="D43" s="83" t="str" cm="1">
+      <c r="D43" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D43" ca="1">IF(OR(IF(OR(A43="", B43="", C43=""), "", INDIRECT("'" &amp; B43 &amp; "'!" &amp; C43))=0, IF(OR(A43="", B43="", C43=""), "", INDIRECT("'" &amp; B43 &amp; "'!" &amp; C43))=""),"",INDIRECT("'" &amp; B43 &amp; "'!" &amp; C43))</f>
-        <v>3.484</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -6948,9 +7127,9 @@
       <c r="C44" s="72" t="s">
         <v>365</v>
       </c>
-      <c r="D44" s="83" t="str" cm="1">
+      <c r="D44" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D44" ca="1">IF(OR(IF(OR(A44="", B44="", C44=""), "", INDIRECT("'" &amp; B44 &amp; "'!" &amp; C44))=0, IF(OR(A44="", B44="", C44=""), "", INDIRECT("'" &amp; B44 &amp; "'!" &amp; C44))=""),"",INDIRECT("'" &amp; B44 &amp; "'!" &amp; C44))</f>
-        <v>3.625</v>
+        <v>#REF!</v>
       </c>
       <c r="F44" t="s">
         <v>366</v>
@@ -6967,9 +7146,9 @@
       <c r="C45" s="72" t="s">
         <v>367</v>
       </c>
-      <c r="D45" s="83" t="str" cm="1">
+      <c r="D45" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D45" ca="1">IF(OR(IF(OR(A45="", B45="", C45=""), "", INDIRECT("'" &amp; B45 &amp; "'!" &amp; C45))=0, IF(OR(A45="", B45="", C45=""), "", INDIRECT("'" &amp; B45 &amp; "'!" &amp; C45))=""),"",INDIRECT("'" &amp; B45 &amp; "'!" &amp; C45))</f>
-        <v>3.769</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -6983,9 +7162,9 @@
       <c r="C46" s="72" t="s">
         <v>368</v>
       </c>
-      <c r="D46" s="83" t="str" cm="1">
+      <c r="D46" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D46" ca="1">IF(OR(IF(OR(A46="", B46="", C46=""), "", INDIRECT("'" &amp; B46 &amp; "'!" &amp; C46))=0, IF(OR(A46="", B46="", C46=""), "", INDIRECT("'" &amp; B46 &amp; "'!" &amp; C46))=""),"",INDIRECT("'" &amp; B46 &amp; "'!" &amp; C46))</f>
-        <v>3.897</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -6999,9 +7178,9 @@
       <c r="C47" s="72" t="s">
         <v>369</v>
       </c>
-      <c r="D47" s="83" t="str" cm="1">
+      <c r="D47" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D47" ca="1">IF(OR(IF(OR(A47="", B47="", C47=""), "", INDIRECT("'" &amp; B47 &amp; "'!" &amp; C47))=0, IF(OR(A47="", B47="", C47=""), "", INDIRECT("'" &amp; B47 &amp; "'!" &amp; C47))=""),"",INDIRECT("'" &amp; B47 &amp; "'!" &amp; C47))</f>
-        <v>3.948</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -7015,9 +7194,9 @@
       <c r="C48" s="72" t="s">
         <v>370</v>
       </c>
-      <c r="D48" s="83" t="str" cm="1">
+      <c r="D48" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D48" ca="1">IF(OR(IF(OR(A48="", B48="", C48=""), "", INDIRECT("'" &amp; B48 &amp; "'!" &amp; C48))=0, IF(OR(A48="", B48="", C48=""), "", INDIRECT("'" &amp; B48 &amp; "'!" &amp; C48))=""),"",INDIRECT("'" &amp; B48 &amp; "'!" &amp; C48))</f>
-        <v>3.993</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -7031,9 +7210,9 @@
       <c r="C49" s="72" t="s">
         <v>371</v>
       </c>
-      <c r="D49" s="83" t="str" cm="1">
+      <c r="D49" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D49" ca="1">IF(OR(IF(OR(A49="", B49="", C49=""), "", INDIRECT("'" &amp; B49 &amp; "'!" &amp; C49))=0, IF(OR(A49="", B49="", C49=""), "", INDIRECT("'" &amp; B49 &amp; "'!" &amp; C49))=""),"",INDIRECT("'" &amp; B49 &amp; "'!" &amp; C49))</f>
-        <v>4.035</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -7047,9 +7226,9 @@
       <c r="C50" s="72" t="s">
         <v>372</v>
       </c>
-      <c r="D50" s="83" t="str" cm="1">
+      <c r="D50" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D50" ca="1">IF(OR(IF(OR(A50="", B50="", C50=""), "", INDIRECT("'" &amp; B50 &amp; "'!" &amp; C50))=0, IF(OR(A50="", B50="", C50=""), "", INDIRECT("'" &amp; B50 &amp; "'!" &amp; C50))=""),"",INDIRECT("'" &amp; B50 &amp; "'!" &amp; C50))</f>
-        <v>4.071</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -7063,9 +7242,9 @@
       <c r="C51" s="72" t="s">
         <v>373</v>
       </c>
-      <c r="D51" s="83" t="str" cm="1">
+      <c r="D51" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D51" ca="1">IF(OR(IF(OR(A51="", B51="", C51=""), "", INDIRECT("'" &amp; B51 &amp; "'!" &amp; C51))=0, IF(OR(A51="", B51="", C51=""), "", INDIRECT("'" &amp; B51 &amp; "'!" &amp; C51))=""),"",INDIRECT("'" &amp; B51 &amp; "'!" &amp; C51))</f>
-        <v>4.091</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -7079,9 +7258,9 @@
       <c r="C52" s="72" t="s">
         <v>374</v>
       </c>
-      <c r="D52" s="83" t="str" cm="1">
+      <c r="D52" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D52" ca="1">IF(OR(IF(OR(A52="", B52="", C52=""), "", INDIRECT("'" &amp; B52 &amp; "'!" &amp; C52))=0, IF(OR(A52="", B52="", C52=""), "", INDIRECT("'" &amp; B52 &amp; "'!" &amp; C52))=""),"",INDIRECT("'" &amp; B52 &amp; "'!" &amp; C52))</f>
-        <v>4.101</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -7095,9 +7274,9 @@
       <c r="C53" s="72" t="s">
         <v>375</v>
       </c>
-      <c r="D53" s="83" t="str" cm="1">
+      <c r="D53" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D53" ca="1">IF(OR(IF(OR(A53="", B53="", C53=""), "", INDIRECT("'" &amp; B53 &amp; "'!" &amp; C53))=0, IF(OR(A53="", B53="", C53=""), "", INDIRECT("'" &amp; B53 &amp; "'!" &amp; C53))=""),"",INDIRECT("'" &amp; B53 &amp; "'!" &amp; C53))</f>
-        <v>4.105</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -7111,9 +7290,9 @@
       <c r="C54" s="72" t="s">
         <v>376</v>
       </c>
-      <c r="D54" s="83" t="str" cm="1">
+      <c r="D54" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D54" ca="1">IF(OR(IF(OR(A54="", B54="", C54=""), "", INDIRECT("'" &amp; B54 &amp; "'!" &amp; C54))=0, IF(OR(A54="", B54="", C54=""), "", INDIRECT("'" &amp; B54 &amp; "'!" &amp; C54))=""),"",INDIRECT("'" &amp; B54 &amp; "'!" &amp; C54))</f>
-        <v>4.122</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -7127,9 +7306,9 @@
       <c r="C55" s="72" t="s">
         <v>377</v>
       </c>
-      <c r="D55" s="83" t="str" cm="1">
+      <c r="D55" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D55" ca="1">IF(OR(IF(OR(A55="", B55="", C55=""), "", INDIRECT("'" &amp; B55 &amp; "'!" &amp; C55))=0, IF(OR(A55="", B55="", C55=""), "", INDIRECT("'" &amp; B55 &amp; "'!" &amp; C55))=""),"",INDIRECT("'" &amp; B55 &amp; "'!" &amp; C55))</f>
-        <v>4.125</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -7143,9 +7322,9 @@
       <c r="C56" s="72" t="s">
         <v>378</v>
       </c>
-      <c r="D56" s="83" t="str" cm="1">
+      <c r="D56" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D56" ca="1">IF(OR(IF(OR(A56="", B56="", C56=""), "", INDIRECT("'" &amp; B56 &amp; "'!" &amp; C56))=0, IF(OR(A56="", B56="", C56=""), "", INDIRECT("'" &amp; B56 &amp; "'!" &amp; C56))=""),"",INDIRECT("'" &amp; B56 &amp; "'!" &amp; C56))</f>
-        <v>4.143</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -7158,9 +7337,9 @@
       <c r="C57" s="72" t="s">
         <v>378</v>
       </c>
-      <c r="D57" s="83" t="str" cm="1">
+      <c r="D57" s="83" t="e" cm="1">
         <f t="array" aca="1" ref="D57" ca="1">IF(OR(IF(OR(A57="", B57="", C57=""), "", INDIRECT("'" &amp; B57 &amp; "'!" &amp; C57))=0, IF(OR(A57="", B57="", C57=""), "", INDIRECT("'" &amp; B57 &amp; "'!" &amp; C57))=""),"",INDIRECT("'" &amp; B57 &amp; "'!" &amp; C57))</f>
-        <v>4.143</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -12247,438 +12426,938 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6B97F7B-59EE-4E8C-BEFF-E0CB54FA4454}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6B97F7B-59EE-4E8C-BEFF-E0CB54FA4454}">
   <sheetPr codeName="Sheet15"/>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="1"/>
     <col min="6" max="6" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="8" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="12.42578125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="134" t="s">
+        <v>438</v>
+      </c>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="102" t="s">
-        <v>411</v>
-      </c>
-      <c r="G1" s="102" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="I2" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C3" s="40" t="s">
         <v>266</v>
       </c>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="F3" s="112"/>
+      <c r="G3" s="112"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C4" s="40" t="s">
         <v>267</v>
-      </c>
-      <c r="F3" s="113"/>
-      <c r="G3" s="112"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>268</v>
       </c>
       <c r="F4" s="113"/>
       <c r="G4" s="112"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I4" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F5" s="113"/>
       <c r="G5" s="112"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I5" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F6" s="113"/>
       <c r="G6" s="112"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I6" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F7" s="113"/>
       <c r="G7" s="112"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F8" s="113"/>
       <c r="G8" s="112"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F9" s="113"/>
       <c r="G9" s="112"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F10" s="113"/>
       <c r="G10" s="112"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F11" s="113"/>
       <c r="G11" s="112"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F12" s="113"/>
       <c r="G12" s="112"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F13" s="113"/>
       <c r="G13" s="112"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F14" s="113"/>
       <c r="G14" s="112"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F15" s="113"/>
       <c r="G15" s="112"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F16" s="113"/>
       <c r="G16" s="112"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F17" s="113"/>
       <c r="G17" s="112"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F18" s="113"/>
       <c r="G18" s="112"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F19" s="113"/>
       <c r="G19" s="112"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F20" s="113"/>
       <c r="G20" s="112"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F21" s="113"/>
       <c r="G21" s="112"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F22" s="113"/>
       <c r="G22" s="112"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F23" s="113"/>
       <c r="G23" s="112"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F24" s="113"/>
       <c r="G24" s="112"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F25" s="113"/>
       <c r="G25" s="112"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F26" s="113"/>
       <c r="G26" s="112"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F27" s="113"/>
       <c r="G27" s="112"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F28" s="113"/>
       <c r="G28" s="112"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F29" s="113"/>
       <c r="G29" s="112"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F30" s="113"/>
       <c r="G30" s="112"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F31" s="113"/>
       <c r="G31" s="112"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>295</v>
+      </c>
       <c r="F32" s="113"/>
-      <c r="G32" s="114"/>
+      <c r="G32" s="112"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F33" s="113"/>
+      <c r="G33" s="114"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="133" t="str">
+        <f>IF($A$121&lt;&gt;"","FROZEN RATES (" &amp; TEXT($A$121, "mm/dd/yyyy hh:mm AM/PM") &amp; ")","FROZEN RATES")</f>
+        <v>FROZEN RATES</v>
+      </c>
+      <c r="B35" s="133"/>
+      <c r="C35" s="133"/>
+      <c r="D35" s="147" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="135" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" s="136" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="136" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="137"/>
+      <c r="B37" s="138"/>
+      <c r="C37" s="139"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="140"/>
+      <c r="B38" s="141"/>
+      <c r="C38" s="142"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="143"/>
+      <c r="B39" s="144"/>
+      <c r="C39" s="145"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="140"/>
+      <c r="B40" s="141"/>
+      <c r="C40" s="142"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="143"/>
+      <c r="B41" s="144"/>
+      <c r="C41" s="145"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="140"/>
+      <c r="B42" s="141"/>
+      <c r="C42" s="142"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="143"/>
+      <c r="B43" s="144"/>
+      <c r="C43" s="145"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="140"/>
+      <c r="B44" s="141"/>
+      <c r="C44" s="142"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="143"/>
+      <c r="B45" s="144"/>
+      <c r="C45" s="145"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="140"/>
+      <c r="B46" s="141"/>
+      <c r="C46" s="142"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="143"/>
+      <c r="B47" s="144"/>
+      <c r="C47" s="145"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="140"/>
+      <c r="B48" s="141"/>
+      <c r="C48" s="142"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="143"/>
+      <c r="B49" s="144"/>
+      <c r="C49" s="145"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="140"/>
+      <c r="B50" s="141"/>
+      <c r="C50" s="142"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="143"/>
+      <c r="B51" s="144"/>
+      <c r="C51" s="145"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="140"/>
+      <c r="B52" s="141"/>
+      <c r="C52" s="142"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="143"/>
+      <c r="B53" s="144"/>
+      <c r="C53" s="145"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="140"/>
+      <c r="B54" s="141"/>
+      <c r="C54" s="142"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="143"/>
+      <c r="B55" s="144"/>
+      <c r="C55" s="145"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="140"/>
+      <c r="B56" s="141"/>
+      <c r="C56" s="142"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="143"/>
+      <c r="B57" s="144"/>
+      <c r="C57" s="145"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="140"/>
+      <c r="B58" s="141"/>
+      <c r="C58" s="142"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="143"/>
+      <c r="B59" s="144"/>
+      <c r="C59" s="145"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="140"/>
+      <c r="B60" s="141"/>
+      <c r="C60" s="142"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="143"/>
+      <c r="B61" s="144"/>
+      <c r="C61" s="145"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="140"/>
+      <c r="B62" s="141"/>
+      <c r="C62" s="142"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="143"/>
+      <c r="B63" s="144"/>
+      <c r="C63" s="145"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="140"/>
+      <c r="B64" s="141"/>
+      <c r="C64" s="142"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="143"/>
+      <c r="B65" s="144"/>
+      <c r="C65" s="145"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="140"/>
+      <c r="B66" s="141"/>
+      <c r="C66" s="142"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67"/>
+      <c r="B67"/>
+      <c r="C67"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68"/>
+      <c r="B68"/>
+      <c r="C68"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69"/>
+      <c r="B69"/>
+      <c r="C69"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70"/>
+      <c r="B70"/>
+      <c r="C70"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71"/>
+      <c r="B71"/>
+      <c r="C71"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72"/>
+      <c r="B72"/>
+      <c r="C72"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73"/>
+      <c r="B73"/>
+      <c r="C73"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74"/>
+      <c r="B74"/>
+      <c r="C74"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75"/>
+      <c r="B75"/>
+      <c r="C75"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76"/>
+      <c r="B76"/>
+      <c r="C76"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77"/>
+      <c r="B77"/>
+      <c r="C77"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78"/>
+      <c r="B78"/>
+      <c r="C78"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79"/>
+      <c r="B79"/>
+      <c r="C79"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80"/>
+      <c r="B80"/>
+      <c r="C80"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81"/>
+      <c r="B81"/>
+      <c r="C81"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83"/>
+      <c r="B83"/>
+      <c r="C83"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84"/>
+      <c r="B84"/>
+      <c r="C84"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85"/>
+      <c r="B85"/>
+      <c r="C85"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86"/>
+      <c r="B86"/>
+      <c r="C86"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87"/>
+      <c r="B87"/>
+      <c r="C87"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88"/>
+      <c r="B88"/>
+      <c r="C88"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89"/>
+      <c r="B89"/>
+      <c r="C89"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90"/>
+      <c r="B90"/>
+      <c r="C90"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91"/>
+      <c r="B91"/>
+      <c r="C91"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92"/>
+      <c r="B92"/>
+      <c r="C92"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93"/>
+      <c r="B93"/>
+      <c r="C93"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94"/>
+      <c r="B94"/>
+      <c r="C94"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95"/>
+      <c r="B95"/>
+      <c r="C95"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96"/>
+      <c r="B96"/>
+      <c r="C96"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97"/>
+      <c r="B97"/>
+      <c r="C97"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98"/>
+      <c r="B98"/>
+      <c r="C98"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100"/>
+      <c r="B100"/>
+      <c r="C100"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103"/>
+      <c r="B103"/>
+      <c r="C103"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105"/>
+      <c r="B105"/>
+      <c r="C105"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106"/>
+      <c r="B106"/>
+      <c r="C106"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107"/>
+      <c r="B107"/>
+      <c r="C107"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108"/>
+      <c r="B108"/>
+      <c r="C108"/>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112"/>
+      <c r="B112"/>
+      <c r="C112"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113"/>
+      <c r="B113"/>
+      <c r="C113"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114"/>
+      <c r="B114"/>
+      <c r="C114"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115"/>
+      <c r="B115"/>
+      <c r="C115"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116"/>
+      <c r="B116"/>
+      <c r="C116"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117"/>
+      <c r="B117"/>
+      <c r="C117"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118"/>
+      <c r="B118"/>
+      <c r="C118"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119"/>
+      <c r="B119"/>
+      <c r="C119"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="146"/>
+      <c r="B120"/>
+      <c r="C120"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <tableParts count="2">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
+  <legacyDrawing r:id="rId2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="19457" r:id="rId3" name="Check Box 1">
+              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0" macro="[1]!ToggleBloombergRatesFreeze">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>19050</xdr:colOff>
+                    <xdr:row>33</xdr:row>
+                    <xdr:rowOff>95250</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>1028700</xdr:colOff>
+                    <xdr:row>35</xdr:row>
+                    <xdr:rowOff>95250</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -32705,36 +33384,62 @@
     </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="EQ10:EU10"/>
-    <mergeCell ref="EP1:EU1"/>
-    <mergeCell ref="EP2:EU2"/>
-    <mergeCell ref="EP3:EU3"/>
-    <mergeCell ref="EQ4:EU4"/>
-    <mergeCell ref="EP5:EU5"/>
-    <mergeCell ref="EQ6:EU6"/>
-    <mergeCell ref="EQ7:EU7"/>
-    <mergeCell ref="EQ8:EU8"/>
-    <mergeCell ref="EQ9:EU9"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="R1:W1"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="S10:W10"/>
-    <mergeCell ref="S7:W7"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="S4:W4"/>
-    <mergeCell ref="R5:W5"/>
-    <mergeCell ref="S6:W6"/>
-    <mergeCell ref="R2:W2"/>
-    <mergeCell ref="R3:W3"/>
+    <mergeCell ref="EA10:EE10"/>
+    <mergeCell ref="DJ1:DO1"/>
+    <mergeCell ref="DJ2:DO2"/>
+    <mergeCell ref="DJ3:DO3"/>
+    <mergeCell ref="DK4:DO4"/>
+    <mergeCell ref="DK6:DO6"/>
+    <mergeCell ref="DK7:DO7"/>
+    <mergeCell ref="DK8:DO8"/>
+    <mergeCell ref="DK9:DO9"/>
+    <mergeCell ref="DJ5:DO5"/>
+    <mergeCell ref="DK10:DO10"/>
+    <mergeCell ref="DZ1:EE1"/>
+    <mergeCell ref="DZ2:EE2"/>
+    <mergeCell ref="DZ3:EE3"/>
+    <mergeCell ref="EA4:EE4"/>
+    <mergeCell ref="DZ5:EE5"/>
+    <mergeCell ref="EA6:EE6"/>
+    <mergeCell ref="EA7:EE7"/>
+    <mergeCell ref="EA8:EE8"/>
+    <mergeCell ref="EA9:EE9"/>
+    <mergeCell ref="CE9:CI9"/>
+    <mergeCell ref="BO10:BS10"/>
+    <mergeCell ref="CU6:CY6"/>
+    <mergeCell ref="CU7:CY7"/>
+    <mergeCell ref="CU8:CY8"/>
+    <mergeCell ref="CU9:CY9"/>
+    <mergeCell ref="CU10:CY10"/>
+    <mergeCell ref="CT1:CY1"/>
+    <mergeCell ref="CT2:CY2"/>
+    <mergeCell ref="CT3:CY3"/>
+    <mergeCell ref="CU4:CY4"/>
+    <mergeCell ref="CT5:CY5"/>
+    <mergeCell ref="AY4:BC4"/>
+    <mergeCell ref="AX5:BC5"/>
+    <mergeCell ref="AY6:BC6"/>
+    <mergeCell ref="AY7:BC7"/>
+    <mergeCell ref="AY8:BC8"/>
+    <mergeCell ref="AY9:BC9"/>
+    <mergeCell ref="CE10:CI10"/>
+    <mergeCell ref="BN1:BS1"/>
+    <mergeCell ref="BN2:BS2"/>
+    <mergeCell ref="BN3:BS3"/>
+    <mergeCell ref="BO4:BS4"/>
+    <mergeCell ref="BN5:BS5"/>
+    <mergeCell ref="BO6:BS6"/>
+    <mergeCell ref="BO7:BS7"/>
+    <mergeCell ref="BO8:BS8"/>
+    <mergeCell ref="BO9:BS9"/>
+    <mergeCell ref="CD1:CI1"/>
+    <mergeCell ref="CD2:CI2"/>
+    <mergeCell ref="CD3:CI3"/>
+    <mergeCell ref="CE4:CI4"/>
+    <mergeCell ref="CD5:CI5"/>
+    <mergeCell ref="CE6:CI6"/>
+    <mergeCell ref="CE7:CI7"/>
+    <mergeCell ref="CE8:CI8"/>
     <mergeCell ref="AY10:BC10"/>
     <mergeCell ref="S53:W53"/>
     <mergeCell ref="S54:W54"/>
@@ -32759,62 +33464,36 @@
     <mergeCell ref="AX1:BC1"/>
     <mergeCell ref="AX2:BC2"/>
     <mergeCell ref="AX3:BC3"/>
-    <mergeCell ref="AY4:BC4"/>
-    <mergeCell ref="AX5:BC5"/>
-    <mergeCell ref="AY6:BC6"/>
-    <mergeCell ref="AY7:BC7"/>
-    <mergeCell ref="AY8:BC8"/>
-    <mergeCell ref="AY9:BC9"/>
-    <mergeCell ref="CE10:CI10"/>
-    <mergeCell ref="BN1:BS1"/>
-    <mergeCell ref="BN2:BS2"/>
-    <mergeCell ref="BN3:BS3"/>
-    <mergeCell ref="BO4:BS4"/>
-    <mergeCell ref="BN5:BS5"/>
-    <mergeCell ref="BO6:BS6"/>
-    <mergeCell ref="BO7:BS7"/>
-    <mergeCell ref="BO8:BS8"/>
-    <mergeCell ref="BO9:BS9"/>
-    <mergeCell ref="CD1:CI1"/>
-    <mergeCell ref="CD2:CI2"/>
-    <mergeCell ref="CD3:CI3"/>
-    <mergeCell ref="CE4:CI4"/>
-    <mergeCell ref="CD5:CI5"/>
-    <mergeCell ref="CE6:CI6"/>
-    <mergeCell ref="CE7:CI7"/>
-    <mergeCell ref="CE8:CI8"/>
-    <mergeCell ref="CE9:CI9"/>
-    <mergeCell ref="BO10:BS10"/>
-    <mergeCell ref="CU6:CY6"/>
-    <mergeCell ref="CU7:CY7"/>
-    <mergeCell ref="CU8:CY8"/>
-    <mergeCell ref="CU9:CY9"/>
-    <mergeCell ref="CU10:CY10"/>
-    <mergeCell ref="CT1:CY1"/>
-    <mergeCell ref="CT2:CY2"/>
-    <mergeCell ref="CT3:CY3"/>
-    <mergeCell ref="CU4:CY4"/>
-    <mergeCell ref="CT5:CY5"/>
-    <mergeCell ref="EA10:EE10"/>
-    <mergeCell ref="DJ1:DO1"/>
-    <mergeCell ref="DJ2:DO2"/>
-    <mergeCell ref="DJ3:DO3"/>
-    <mergeCell ref="DK4:DO4"/>
-    <mergeCell ref="DK6:DO6"/>
-    <mergeCell ref="DK7:DO7"/>
-    <mergeCell ref="DK8:DO8"/>
-    <mergeCell ref="DK9:DO9"/>
-    <mergeCell ref="DJ5:DO5"/>
-    <mergeCell ref="DK10:DO10"/>
-    <mergeCell ref="DZ1:EE1"/>
-    <mergeCell ref="DZ2:EE2"/>
-    <mergeCell ref="DZ3:EE3"/>
-    <mergeCell ref="EA4:EE4"/>
-    <mergeCell ref="DZ5:EE5"/>
-    <mergeCell ref="EA6:EE6"/>
-    <mergeCell ref="EA7:EE7"/>
-    <mergeCell ref="EA8:EE8"/>
-    <mergeCell ref="EA9:EE9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="R1:W1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="S10:W10"/>
+    <mergeCell ref="S7:W7"/>
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="S4:W4"/>
+    <mergeCell ref="R5:W5"/>
+    <mergeCell ref="S6:W6"/>
+    <mergeCell ref="R2:W2"/>
+    <mergeCell ref="R3:W3"/>
+    <mergeCell ref="EQ10:EU10"/>
+    <mergeCell ref="EP1:EU1"/>
+    <mergeCell ref="EP2:EU2"/>
+    <mergeCell ref="EP3:EU3"/>
+    <mergeCell ref="EQ4:EU4"/>
+    <mergeCell ref="EP5:EU5"/>
+    <mergeCell ref="EQ6:EU6"/>
+    <mergeCell ref="EQ7:EU7"/>
+    <mergeCell ref="EQ8:EU8"/>
+    <mergeCell ref="EQ9:EU9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
